--- a/docs/Logic Requirements/Ageipelago Vlad Dracula.xlsx
+++ b/docs/Logic Requirements/Ageipelago Vlad Dracula.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\stefb\OneDrive\Desktop\Logic Requirements\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6A43582F-2A6F-4059-BEC6-043127A63A94}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{11EA5A38-D17B-4B49-BA05-955747713689}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="4" xr2:uid="{B80992DC-780F-4856-A6B0-D26FA95FCBC0}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{B80992DC-780F-4856-A6B0-D26FA95FCBC0}"/>
   </bookViews>
   <sheets>
     <sheet name="Vlad Dracula" sheetId="1" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="744" uniqueCount="247">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="905" uniqueCount="261">
   <si>
     <t>Scenario</t>
   </si>
@@ -105,12 +105,6 @@
   </si>
   <si>
     <t>The Night Falls</t>
-  </si>
-  <si>
-    <t>1 Hussar (Gaia)
-1 Hussar, 3 Long Swordsmen (Gaia) x2
-1 Hussar, 2 Hand Cannoneers (Gaia) x2
-1 Transport Ship, 2 Heavy Demolition Ships (Gaia)</t>
   </si>
   <si>
     <t>9 Hussars
@@ -2712,114 +2706,6 @@
   </si>
   <si>
     <r>
-      <t xml:space="preserve">Defeat the Iinitial </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <color rgb="FF0070C0"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>Enemy Force</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">
-Defeat the </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <color rgb="FF7030A0"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>Enemy Force</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> withing </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <color theme="0" tint="-0.499984740745262"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>Sabac</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">
-Enter the </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <color rgb="FFFFFF00"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>Wallachian Town</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">
-Defeat </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <color rgb="FF0070C0"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>Basarab Laiota</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">
-Defeat </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <color rgb="FF7030A0"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>Ottoman Empire</t>
-    </r>
-  </si>
-  <si>
-    <r>
       <t>The Bridge to the North is repaired
 The Stones blocking the Way East are removed and the Bridge to the East is repaired
 5 Villagers, 1 Town Center, 3 Long Swordsmen, 3 Pikemen, 2 Crossbowmen, 1 Knight, 1 Monk, Misc, Buildings, 1000 Food, 1000 Wood, 1000 Gold, 500 Stone (</t>
@@ -4573,9 +4459,6 @@
     <t>Fence</t>
   </si>
   <si>
-    <t>Likely unreachable</t>
-  </si>
-  <si>
     <t>Knights</t>
   </si>
   <si>
@@ -4845,6 +4728,186 @@
       </rPr>
       <t>:
 All Military Technologies are researched automatically</t>
+    </r>
+  </si>
+  <si>
+    <t>Starting Units</t>
+  </si>
+  <si>
+    <t>Starting Buildings</t>
+  </si>
+  <si>
+    <t>Item-Units</t>
+  </si>
+  <si>
+    <t>Item-Buildings</t>
+  </si>
+  <si>
+    <t>Vlad Dracula</t>
+  </si>
+  <si>
+    <r>
+      <t>1 Hussar (Gaia)
+1 Hussar, 3 Long Swordsmen (Gaia) x2
+1 Hussar, 2 Hand Cannoneers (Gaia) x2
+1 Transport Ship, 2 Heavy Demolition Ships (Gaia)
+5 Long Swordsmen, 3 Hand Cannoneers, (</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color rgb="FFFFFF00"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>Wallachian Voivods</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>)</t>
+    </r>
+  </si>
+  <si>
+    <t>Monk (Only on Standard)</t>
+  </si>
+  <si>
+    <t>Mangonel</t>
+  </si>
+  <si>
+    <t>Heavy Demolition Ship</t>
+  </si>
+  <si>
+    <t>Vlad Dracule</t>
+  </si>
+  <si>
+    <t>Heavy Scorpion</t>
+  </si>
+  <si>
+    <t>Transport required</t>
+  </si>
+  <si>
+    <t>8 Paladins, 6 Hussars, 8 Elite Magyar Huszars, 8 Heavy Cavalry Archers, 1 Transport Ship</t>
+  </si>
+  <si>
+    <t>Elite Magyar Huszars</t>
+  </si>
+  <si>
+    <t>Atchery Range</t>
+  </si>
+  <si>
+    <t>Arbalester</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Defeat the initial </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color rgb="FF0070C0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>Enemy Force</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+Defeat the </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color rgb="FF7030A0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>Enemy Force</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> withing </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="0" tint="-0.499984740745262"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>Sabac</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+Enter the </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color rgb="FFFFFF00"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>Wallachian Town</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+Defeat </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color rgb="FF0070C0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>Basarab Laiota</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+Defeat </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color rgb="FF7030A0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>Ottoman Empire</t>
     </r>
   </si>
 </sst>
@@ -5020,7 +5083,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="11">
+  <borders count="12">
     <border>
       <left/>
       <right/>
@@ -5154,11 +5217,22 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="41">
+  <cellXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -5259,9 +5333,6 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -5278,6 +5349,33 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -5675,41 +5773,41 @@
         <v>16</v>
       </c>
       <c r="C4" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="D4" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="E4" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="D4" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="E4" s="6" t="s">
+      <c r="F4" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="G4" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="F4" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="G4" s="6" t="s">
-        <v>29</v>
-      </c>
       <c r="H4" s="6" t="s">
-        <v>21</v>
+        <v>249</v>
       </c>
       <c r="I4" s="7"/>
       <c r="J4" s="7" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="K4" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="L4" s="7" t="s">
         <v>23</v>
-      </c>
-      <c r="L4" s="7" t="s">
-        <v>24</v>
       </c>
       <c r="M4" s="7"/>
       <c r="N4" s="7" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="O4" s="7"/>
       <c r="P4" s="7"/>
       <c r="Q4" s="7" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="5" spans="2:17" ht="409.6" thickBot="1" x14ac:dyDescent="0.3">
@@ -5717,49 +5815,49 @@
         <v>17</v>
       </c>
       <c r="C5" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="D5" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="E5" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="F5" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="G5" s="9" t="s">
         <v>35</v>
       </c>
-      <c r="D5" s="9" t="s">
+      <c r="H5" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="I5" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="J5" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="K5" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="L5" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="E5" s="9" t="s">
-        <v>37</v>
-      </c>
-      <c r="F5" s="9" t="s">
-        <v>32</v>
-      </c>
-      <c r="G5" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="H5" s="9" t="s">
-        <v>34</v>
-      </c>
-      <c r="I5" s="10" t="s">
-        <v>33</v>
-      </c>
-      <c r="J5" s="7" t="s">
-        <v>42</v>
-      </c>
-      <c r="K5" s="7" t="s">
+      <c r="M5" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="L5" s="7" t="s">
+      <c r="N5" s="7" t="s">
         <v>39</v>
       </c>
-      <c r="M5" s="7" t="s">
+      <c r="O5" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="P5" s="7" t="s">
         <v>44</v>
       </c>
-      <c r="N5" s="7" t="s">
-        <v>40</v>
-      </c>
-      <c r="O5" s="7" t="s">
-        <v>41</v>
-      </c>
-      <c r="P5" s="7" t="s">
-        <v>45</v>
-      </c>
       <c r="Q5" s="7" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="6" spans="2:17" ht="409.6" thickBot="1" x14ac:dyDescent="0.3">
@@ -5767,47 +5865,47 @@
         <v>18</v>
       </c>
       <c r="C6" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="D6" s="9" t="s">
         <v>49</v>
       </c>
-      <c r="D6" s="9" t="s">
+      <c r="E6" s="9" t="s">
+        <v>47</v>
+      </c>
+      <c r="F6" s="9" t="s">
+        <v>46</v>
+      </c>
+      <c r="G6" s="9" t="s">
         <v>50</v>
       </c>
-      <c r="E6" s="9" t="s">
-        <v>48</v>
-      </c>
-      <c r="F6" s="9" t="s">
-        <v>47</v>
-      </c>
-      <c r="G6" s="9" t="s">
+      <c r="H6" s="9" t="s">
+        <v>56</v>
+      </c>
+      <c r="I6" s="10" t="s">
         <v>51</v>
       </c>
-      <c r="H6" s="9" t="s">
-        <v>57</v>
-      </c>
-      <c r="I6" s="10" t="s">
-        <v>52</v>
-      </c>
       <c r="J6" s="7" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="K6" s="7"/>
       <c r="L6" s="7" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="M6" s="7" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="N6" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="O6" s="7" t="s">
         <v>54</v>
       </c>
-      <c r="O6" s="7" t="s">
+      <c r="P6" s="7" t="s">
         <v>55</v>
       </c>
-      <c r="P6" s="7" t="s">
-        <v>56</v>
-      </c>
       <c r="Q6" s="7" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="7" spans="2:17" ht="409.6" thickBot="1" x14ac:dyDescent="0.3">
@@ -5815,43 +5913,45 @@
         <v>19</v>
       </c>
       <c r="C7" s="8" t="s">
+        <v>59</v>
+      </c>
+      <c r="D7" s="9" t="s">
+        <v>65</v>
+      </c>
+      <c r="E7" s="9" t="s">
         <v>60</v>
       </c>
-      <c r="D7" s="9" t="s">
-        <v>66</v>
-      </c>
-      <c r="E7" s="9" t="s">
-        <v>61</v>
-      </c>
       <c r="F7" s="9" t="s">
-        <v>59</v>
-      </c>
-      <c r="G7" s="9"/>
+        <v>58</v>
+      </c>
+      <c r="G7" s="9" t="s">
+        <v>256</v>
+      </c>
       <c r="H7" s="9" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="I7" s="10" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="J7" s="7"/>
       <c r="K7" s="7"/>
       <c r="L7" s="7" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="M7" s="7" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="N7" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="O7" s="7" t="s">
         <v>62</v>
       </c>
-      <c r="O7" s="7" t="s">
-        <v>63</v>
-      </c>
       <c r="P7" s="7" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="Q7" s="7" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="8" spans="2:17" ht="409.6" thickBot="1" x14ac:dyDescent="0.3">
@@ -5859,44 +5959,44 @@
         <v>20</v>
       </c>
       <c r="C8" s="8" t="s">
+        <v>260</v>
+      </c>
+      <c r="D8" s="9" t="s">
+        <v>226</v>
+      </c>
+      <c r="E8" s="9" t="s">
+        <v>73</v>
+      </c>
+      <c r="F8" s="9" t="s">
+        <v>68</v>
+      </c>
+      <c r="G8" s="9" t="s">
+        <v>71</v>
+      </c>
+      <c r="H8" s="9" t="s">
         <v>72</v>
       </c>
-      <c r="D8" s="9" t="s">
-        <v>229</v>
-      </c>
-      <c r="E8" s="9" t="s">
-        <v>75</v>
-      </c>
-      <c r="F8" s="9" t="s">
-        <v>69</v>
-      </c>
-      <c r="G8" s="9" t="s">
-        <v>73</v>
-      </c>
-      <c r="H8" s="9" t="s">
+      <c r="I8" s="10" t="s">
+        <v>70</v>
+      </c>
+      <c r="J8" s="7" t="s">
         <v>74</v>
-      </c>
-      <c r="I8" s="10" t="s">
-        <v>71</v>
-      </c>
-      <c r="J8" s="7" t="s">
-        <v>76</v>
       </c>
       <c r="K8" s="7"/>
       <c r="L8" s="7" t="s">
+        <v>75</v>
+      </c>
+      <c r="M8" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="N8" s="7" t="s">
         <v>77</v>
       </c>
-      <c r="M8" s="7" t="s">
-        <v>78</v>
-      </c>
-      <c r="N8" s="7" t="s">
-        <v>79</v>
-      </c>
       <c r="O8" s="7" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="P8" s="7" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="Q8" s="7"/>
     </row>
@@ -5930,93 +6030,94 @@
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="4" width="22.5703125" customWidth="1"/>
+    <col min="5" max="5" width="22.7109375" customWidth="1"/>
     <col min="7" max="8" width="22.5703125" customWidth="1"/>
     <col min="11" max="12" width="22.5703125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="2" spans="2:12" ht="47.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="35" t="s">
-        <v>230</v>
-      </c>
-      <c r="C2" s="36"/>
-      <c r="D2" s="37"/>
+      <c r="B2" s="34" t="s">
+        <v>227</v>
+      </c>
+      <c r="C2" s="35"/>
+      <c r="D2" s="36"/>
       <c r="G2" s="2" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="H2" s="2" t="s">
         <v>15</v>
       </c>
       <c r="K2" s="2" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="L2" s="2" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="3" spans="2:12" ht="24" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B3" s="38" t="s">
-        <v>237</v>
-      </c>
-      <c r="C3" s="39"/>
-      <c r="D3" s="40"/>
+      <c r="B3" s="37" t="s">
+        <v>234</v>
+      </c>
+      <c r="C3" s="38"/>
+      <c r="D3" s="39"/>
       <c r="G3" s="6" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="H3" s="6" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="K3" s="21" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="L3" s="6" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
     </row>
     <row r="4" spans="2:12" ht="24" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B4" s="2" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>234</v>
+        <v>231</v>
       </c>
       <c r="G4" s="9" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="H4" s="9" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="K4" s="13" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="L4" s="9" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
     </row>
     <row r="5" spans="2:12" ht="75" x14ac:dyDescent="0.25">
       <c r="B5" s="31" t="s">
-        <v>236</v>
+        <v>233</v>
       </c>
       <c r="C5" s="31" t="s">
+        <v>235</v>
+      </c>
+      <c r="D5" s="31" t="s">
         <v>238</v>
       </c>
-      <c r="D5" s="31" t="s">
-        <v>241</v>
-      </c>
       <c r="G5" s="9" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="H5" s="9" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="K5" s="13" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="L5" s="9" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
     </row>
     <row r="6" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
@@ -6024,339 +6125,443 @@
       <c r="C6" s="32"/>
       <c r="D6" s="33"/>
       <c r="G6" s="13" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="H6" s="9" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="K6" s="13" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="L6" s="9" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="7" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="7" spans="2:12" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B7" s="32"/>
       <c r="C7" s="32"/>
       <c r="D7" s="33"/>
       <c r="G7" s="13" t="s">
+        <v>88</v>
+      </c>
+      <c r="H7" s="9" t="s">
+        <v>81</v>
+      </c>
+      <c r="K7" s="13" t="s">
+        <v>136</v>
+      </c>
+      <c r="L7" s="9" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="8" spans="2:12" ht="47.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B8" s="2" t="s">
+        <v>244</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>245</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>246</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>247</v>
+      </c>
+      <c r="G8" s="13" t="s">
         <v>90</v>
       </c>
-      <c r="H7" s="9" t="s">
+      <c r="H8" s="9" t="s">
+        <v>81</v>
+      </c>
+      <c r="K8" s="16" t="s">
+        <v>137</v>
+      </c>
+      <c r="L8" s="9" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="9" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B9" s="31" t="s">
+        <v>248</v>
+      </c>
+      <c r="C9" s="40"/>
+      <c r="D9" s="42" t="s">
+        <v>157</v>
+      </c>
+      <c r="E9" s="31" t="s">
+        <v>87</v>
+      </c>
+      <c r="G9" s="13" t="s">
+        <v>91</v>
+      </c>
+      <c r="H9" s="9" t="s">
+        <v>81</v>
+      </c>
+      <c r="K9" s="16" t="s">
+        <v>82</v>
+      </c>
+      <c r="L9" s="9" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="10" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B10" s="31" t="s">
+        <v>157</v>
+      </c>
+      <c r="C10" s="40"/>
+      <c r="D10" s="31" t="s">
+        <v>106</v>
+      </c>
+      <c r="E10" s="31" t="s">
+        <v>85</v>
+      </c>
+      <c r="G10" s="13" t="s">
+        <v>81</v>
+      </c>
+      <c r="H10" s="9" t="s">
+        <v>81</v>
+      </c>
+      <c r="K10" s="16" t="s">
+        <v>84</v>
+      </c>
+      <c r="L10" s="9" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="11" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B11" s="31" t="s">
+        <v>118</v>
+      </c>
+      <c r="C11" s="40"/>
+      <c r="D11" s="42" t="s">
+        <v>157</v>
+      </c>
+      <c r="E11" s="40"/>
+      <c r="G11" s="13" t="s">
+        <v>118</v>
+      </c>
+      <c r="H11" s="9" t="s">
+        <v>81</v>
+      </c>
+      <c r="K11" s="16" t="s">
+        <v>138</v>
+      </c>
+      <c r="L11" s="9" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="12" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B12" s="31" t="s">
+        <v>123</v>
+      </c>
+      <c r="C12" s="40"/>
+      <c r="D12" s="41" t="s">
+        <v>157</v>
+      </c>
+      <c r="E12" s="40"/>
+      <c r="G12" s="13" t="s">
+        <v>95</v>
+      </c>
+      <c r="H12" s="9" t="s">
+        <v>81</v>
+      </c>
+      <c r="K12" s="16" t="s">
+        <v>105</v>
+      </c>
+      <c r="L12" s="9" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="13" spans="2:12" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="B13" s="31" t="s">
+        <v>250</v>
+      </c>
+      <c r="C13" s="40"/>
+      <c r="D13" s="42" t="s">
+        <v>118</v>
+      </c>
+      <c r="E13" s="40"/>
+      <c r="G13" s="13" t="s">
+        <v>119</v>
+      </c>
+      <c r="H13" s="9" t="s">
+        <v>81</v>
+      </c>
+      <c r="K13" s="16" t="s">
+        <v>114</v>
+      </c>
+      <c r="L13" s="9" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="14" spans="2:12" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="B14" s="40"/>
+      <c r="C14" s="40"/>
+      <c r="D14" s="41" t="s">
+        <v>106</v>
+      </c>
+      <c r="E14" s="40"/>
+      <c r="G14" s="13" t="s">
+        <v>131</v>
+      </c>
+      <c r="H14" s="9" t="s">
+        <v>81</v>
+      </c>
+      <c r="K14" s="17" t="s">
+        <v>94</v>
+      </c>
+      <c r="L14" s="9" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="15" spans="2:12" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="B15" s="40"/>
+      <c r="C15" s="40"/>
+      <c r="D15" s="42" t="s">
+        <v>118</v>
+      </c>
+      <c r="E15" s="40"/>
+      <c r="G15" s="13" t="s">
+        <v>130</v>
+      </c>
+      <c r="H15" s="9" t="s">
+        <v>81</v>
+      </c>
+      <c r="K15" s="17" t="s">
+        <v>98</v>
+      </c>
+      <c r="L15" s="9" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="16" spans="2:12" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="B16" s="40"/>
+      <c r="C16" s="40"/>
+      <c r="D16" s="41" t="s">
+        <v>106</v>
+      </c>
+      <c r="E16" s="40"/>
+      <c r="G16" s="16" t="s">
+        <v>129</v>
+      </c>
+      <c r="H16" s="9" t="s">
+        <v>81</v>
+      </c>
+      <c r="K16" s="17" t="s">
+        <v>108</v>
+      </c>
+      <c r="L16" s="9" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="17" spans="2:12" ht="75" x14ac:dyDescent="0.25">
+      <c r="B17" s="40"/>
+      <c r="C17" s="40"/>
+      <c r="D17" s="42" t="s">
+        <v>118</v>
+      </c>
+      <c r="E17" s="40"/>
+      <c r="G17" s="16" t="s">
+        <v>128</v>
+      </c>
+      <c r="H17" s="9" t="s">
+        <v>81</v>
+      </c>
+      <c r="K17" s="17" t="s">
+        <v>97</v>
+      </c>
+      <c r="L17" s="9" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="18" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B18" s="40"/>
+      <c r="C18" s="40"/>
+      <c r="D18" s="31" t="s">
+        <v>102</v>
+      </c>
+      <c r="E18" s="40"/>
+      <c r="G18" s="16" t="s">
+        <v>102</v>
+      </c>
+      <c r="H18" s="9" t="s">
+        <v>81</v>
+      </c>
+      <c r="K18" s="14" t="s">
+        <v>115</v>
+      </c>
+      <c r="L18" s="9" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="19" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B19" s="40"/>
+      <c r="C19" s="40"/>
+      <c r="D19" s="41" t="s">
+        <v>106</v>
+      </c>
+      <c r="E19" s="40"/>
+      <c r="G19" s="17" t="s">
+        <v>120</v>
+      </c>
+      <c r="H19" s="9" t="s">
+        <v>81</v>
+      </c>
+      <c r="K19" s="14" t="s">
+        <v>87</v>
+      </c>
+      <c r="L19" s="9" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="20" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B20" s="40"/>
+      <c r="C20" s="40"/>
+      <c r="D20" s="42" t="s">
+        <v>91</v>
+      </c>
+      <c r="E20" s="40"/>
+      <c r="G20" s="17" t="s">
+        <v>121</v>
+      </c>
+      <c r="H20" s="9" t="s">
+        <v>81</v>
+      </c>
+      <c r="K20" s="14" t="s">
         <v>83</v>
       </c>
-      <c r="K7" s="13" t="s">
-        <v>138</v>
-      </c>
-      <c r="L7" s="9" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="8" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B8" s="34"/>
-      <c r="C8" s="34"/>
-      <c r="D8" s="33"/>
-      <c r="G8" s="13" t="s">
-        <v>92</v>
-      </c>
-      <c r="H8" s="9" t="s">
-        <v>83</v>
-      </c>
-      <c r="K8" s="16" t="s">
+      <c r="L20" s="9" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="21" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B21" s="40"/>
+      <c r="C21" s="40"/>
+      <c r="D21" s="41" t="s">
+        <v>88</v>
+      </c>
+      <c r="E21" s="40"/>
+      <c r="G21" s="17" t="s">
+        <v>122</v>
+      </c>
+      <c r="H21" s="9" t="s">
+        <v>81</v>
+      </c>
+      <c r="K21" s="14" t="s">
+        <v>85</v>
+      </c>
+      <c r="L21" s="9" t="s">
         <v>139</v>
       </c>
-      <c r="L8" s="9" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="9" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B9" s="32"/>
-      <c r="C9" s="32"/>
-      <c r="D9" s="33"/>
-      <c r="G9" s="13" t="s">
-        <v>93</v>
-      </c>
-      <c r="H9" s="9" t="s">
-        <v>83</v>
-      </c>
-      <c r="K9" s="16" t="s">
-        <v>84</v>
-      </c>
-      <c r="L9" s="9" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="10" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B10" s="32"/>
-      <c r="C10" s="32"/>
-      <c r="D10" s="33"/>
-      <c r="G10" s="13" t="s">
-        <v>83</v>
-      </c>
-      <c r="H10" s="9" t="s">
-        <v>83</v>
-      </c>
-      <c r="K10" s="16" t="s">
-        <v>86</v>
-      </c>
-      <c r="L10" s="9" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="11" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B11" s="34"/>
-      <c r="C11" s="34"/>
-      <c r="D11" s="33"/>
-      <c r="G11" s="13" t="s">
-        <v>120</v>
-      </c>
-      <c r="H11" s="9" t="s">
-        <v>83</v>
-      </c>
-      <c r="K11" s="16" t="s">
-        <v>140</v>
-      </c>
-      <c r="L11" s="9" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="12" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B12" s="32"/>
-      <c r="C12" s="32"/>
-      <c r="D12" s="33"/>
-      <c r="G12" s="13" t="s">
-        <v>97</v>
-      </c>
-      <c r="H12" s="9" t="s">
-        <v>83</v>
-      </c>
-      <c r="K12" s="16" t="s">
-        <v>107</v>
-      </c>
-      <c r="L12" s="9" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="13" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B13" s="32"/>
-      <c r="C13" s="32"/>
-      <c r="D13" s="33"/>
-      <c r="G13" s="13" t="s">
-        <v>121</v>
-      </c>
-      <c r="H13" s="9" t="s">
-        <v>83</v>
-      </c>
-      <c r="K13" s="16" t="s">
-        <v>116</v>
-      </c>
-      <c r="L13" s="9" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="14" spans="2:12" ht="37.5" x14ac:dyDescent="0.25">
-      <c r="B14" s="34"/>
-      <c r="C14" s="34"/>
-      <c r="D14" s="33"/>
-      <c r="G14" s="13" t="s">
-        <v>133</v>
-      </c>
-      <c r="H14" s="9" t="s">
-        <v>83</v>
-      </c>
-      <c r="K14" s="17" t="s">
-        <v>96</v>
-      </c>
-      <c r="L14" s="9" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="15" spans="2:12" ht="37.5" x14ac:dyDescent="0.25">
-      <c r="B15" s="32"/>
-      <c r="C15" s="32"/>
-      <c r="D15" s="33"/>
-      <c r="G15" s="13" t="s">
-        <v>132</v>
-      </c>
-      <c r="H15" s="9" t="s">
-        <v>83</v>
-      </c>
-      <c r="K15" s="17" t="s">
-        <v>100</v>
-      </c>
-      <c r="L15" s="9" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="16" spans="2:12" ht="37.5" x14ac:dyDescent="0.25">
-      <c r="B16" s="32"/>
-      <c r="C16" s="32"/>
-      <c r="D16" s="33"/>
-      <c r="G16" s="16" t="s">
-        <v>131</v>
-      </c>
-      <c r="H16" s="9" t="s">
-        <v>83</v>
-      </c>
-      <c r="K16" s="17" t="s">
-        <v>110</v>
-      </c>
-      <c r="L16" s="9" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="17" spans="7:12" ht="75" x14ac:dyDescent="0.25">
-      <c r="G17" s="16" t="s">
-        <v>130</v>
-      </c>
-      <c r="H17" s="9" t="s">
-        <v>83</v>
-      </c>
-      <c r="K17" s="17" t="s">
-        <v>99</v>
-      </c>
-      <c r="L17" s="9" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="18" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G18" s="16" t="s">
-        <v>104</v>
-      </c>
-      <c r="H18" s="9" t="s">
-        <v>83</v>
-      </c>
-      <c r="K18" s="14" t="s">
-        <v>117</v>
-      </c>
-      <c r="L18" s="9" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="19" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G19" s="17" t="s">
-        <v>122</v>
-      </c>
-      <c r="H19" s="9" t="s">
-        <v>83</v>
-      </c>
-      <c r="K19" s="14" t="s">
-        <v>89</v>
-      </c>
-      <c r="L19" s="9" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="20" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G20" s="17" t="s">
+    </row>
+    <row r="22" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B22" s="40"/>
+      <c r="C22" s="40"/>
+      <c r="D22" s="42" t="s">
+        <v>90</v>
+      </c>
+      <c r="E22" s="40"/>
+      <c r="G22" s="17" t="s">
         <v>123</v>
       </c>
-      <c r="H20" s="9" t="s">
-        <v>83</v>
-      </c>
-      <c r="K20" s="14" t="s">
-        <v>85</v>
-      </c>
-      <c r="L20" s="9" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="21" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G21" s="17" t="s">
+      <c r="H22" s="9" t="s">
+        <v>81</v>
+      </c>
+      <c r="K22" s="18" t="s">
+        <v>113</v>
+      </c>
+      <c r="L22" s="19" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="23" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B23" s="40"/>
+      <c r="C23" s="40"/>
+      <c r="D23" s="41" t="s">
+        <v>88</v>
+      </c>
+      <c r="E23" s="40"/>
+      <c r="G23" s="14" t="s">
         <v>124</v>
       </c>
-      <c r="H21" s="9" t="s">
-        <v>83</v>
-      </c>
-      <c r="K21" s="14" t="s">
-        <v>87</v>
-      </c>
-      <c r="L21" s="9" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="22" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G22" s="17" t="s">
-        <v>125</v>
-      </c>
-      <c r="H22" s="9" t="s">
-        <v>83</v>
-      </c>
-      <c r="K22" s="18" t="s">
-        <v>115</v>
-      </c>
-      <c r="L22" s="19" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="23" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G23" s="14" t="s">
-        <v>126</v>
-      </c>
       <c r="H23" s="9" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="K23" s="15"/>
       <c r="L23" s="15"/>
     </row>
-    <row r="24" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="24" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B24" s="40"/>
+      <c r="C24" s="40"/>
+      <c r="D24" s="42" t="s">
+        <v>90</v>
+      </c>
+      <c r="E24" s="40"/>
       <c r="G24" s="14" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="H24" s="9" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="K24" s="20"/>
       <c r="L24" s="20"/>
     </row>
-    <row r="25" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="25" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="D25" s="31" t="s">
+        <v>251</v>
+      </c>
       <c r="G25" s="14" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="H25" s="9" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="K25" s="20"/>
       <c r="L25" s="20"/>
     </row>
-    <row r="26" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="26" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="D26" s="41" t="s">
+        <v>209</v>
+      </c>
       <c r="G26" s="20"/>
       <c r="H26" s="20"/>
       <c r="K26" s="20"/>
       <c r="L26" s="20"/>
     </row>
-    <row r="27" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="27" spans="2:12" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="D27" s="31" t="s">
+        <v>252</v>
+      </c>
       <c r="G27" s="20"/>
       <c r="H27" s="20"/>
       <c r="K27" s="20"/>
       <c r="L27" s="20"/>
     </row>
-    <row r="28" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="28" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G28" s="20"/>
       <c r="H28" s="20"/>
       <c r="K28" s="20"/>
       <c r="L28" s="20"/>
     </row>
-    <row r="29" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="29" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G29" s="20"/>
       <c r="H29" s="20"/>
       <c r="K29" s="20"/>
       <c r="L29" s="20"/>
     </row>
-    <row r="30" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="30" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G30" s="20"/>
       <c r="H30" s="20"/>
       <c r="K30" s="20"/>
       <c r="L30" s="20"/>
     </row>
-    <row r="31" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="31" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G31" s="20"/>
       <c r="H31" s="20"/>
       <c r="K31" s="20"/>
       <c r="L31" s="20"/>
     </row>
-    <row r="32" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="32" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G32" s="20"/>
       <c r="H32" s="20"/>
       <c r="K32" s="20"/>
@@ -6493,97 +6698,98 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{66D5B1F3-605B-4EBE-ADC3-86093F9414AB}">
-  <dimension ref="B1:L52"/>
+  <dimension ref="B1:L66"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="4" width="22.5703125" customWidth="1"/>
+    <col min="5" max="5" width="22.85546875" customWidth="1"/>
     <col min="7" max="8" width="22.5703125" customWidth="1"/>
     <col min="11" max="12" width="22.5703125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="2" spans="2:12" ht="47.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="35" t="s">
-        <v>230</v>
-      </c>
-      <c r="C2" s="36"/>
-      <c r="D2" s="37"/>
+      <c r="B2" s="34" t="s">
+        <v>227</v>
+      </c>
+      <c r="C2" s="35"/>
+      <c r="D2" s="36"/>
       <c r="G2" s="2" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="H2" s="2" t="s">
         <v>15</v>
       </c>
       <c r="K2" s="2" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="L2" s="2" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="3" spans="2:12" ht="24" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B3" s="38" t="s">
-        <v>231</v>
-      </c>
-      <c r="C3" s="39"/>
-      <c r="D3" s="40"/>
+      <c r="B3" s="37" t="s">
+        <v>228</v>
+      </c>
+      <c r="C3" s="38"/>
+      <c r="D3" s="39"/>
       <c r="G3" s="22" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="H3" s="6" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="K3" s="22" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="L3" s="6" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
     </row>
     <row r="4" spans="2:12" ht="24" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B4" s="2" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>234</v>
+        <v>231</v>
       </c>
       <c r="G4" s="16" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="H4" s="9" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="K4" s="16" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="L4" s="9" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
     </row>
     <row r="5" spans="2:12" ht="150" x14ac:dyDescent="0.25">
       <c r="B5" s="31" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="C5" s="31" t="s">
-        <v>235</v>
+        <v>232</v>
       </c>
       <c r="D5" s="31" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="G5" s="16" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="H5" s="9" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="K5" s="16" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="L5" s="9" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
     </row>
     <row r="6" spans="2:12" ht="37.5" x14ac:dyDescent="0.25">
@@ -6591,563 +6797,796 @@
       <c r="C6" s="32"/>
       <c r="D6" s="33"/>
       <c r="G6" s="16" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="H6" s="9" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="K6" s="16" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="L6" s="9" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="7" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="7" spans="2:12" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B7" s="32"/>
       <c r="C7" s="32"/>
       <c r="D7" s="33"/>
       <c r="G7" s="16" t="s">
+        <v>141</v>
+      </c>
+      <c r="H7" s="9" t="s">
+        <v>81</v>
+      </c>
+      <c r="K7" s="16" t="s">
+        <v>115</v>
+      </c>
+      <c r="L7" s="9" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="8" spans="2:12" ht="47.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B8" s="2" t="s">
+        <v>244</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>245</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>246</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>247</v>
+      </c>
+      <c r="G8" s="16" t="s">
+        <v>142</v>
+      </c>
+      <c r="H8" s="9" t="s">
+        <v>81</v>
+      </c>
+      <c r="K8" s="16" t="s">
+        <v>137</v>
+      </c>
+      <c r="L8" s="9" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="9" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B9" s="31" t="s">
+        <v>253</v>
+      </c>
+      <c r="C9" s="40"/>
+      <c r="D9" s="42" t="s">
+        <v>104</v>
+      </c>
+      <c r="E9" s="31" t="s">
+        <v>101</v>
+      </c>
+      <c r="G9" s="16" t="s">
+        <v>106</v>
+      </c>
+      <c r="H9" s="9" t="s">
+        <v>81</v>
+      </c>
+      <c r="K9" s="16" t="s">
+        <v>84</v>
+      </c>
+      <c r="L9" s="9" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="10" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B10" s="31" t="s">
+        <v>99</v>
+      </c>
+      <c r="C10" s="40"/>
+      <c r="D10" s="42" t="s">
+        <v>208</v>
+      </c>
+      <c r="E10" s="42" t="s">
+        <v>96</v>
+      </c>
+      <c r="G10" s="16" t="s">
+        <v>88</v>
+      </c>
+      <c r="H10" s="9" t="s">
+        <v>81</v>
+      </c>
+      <c r="K10" s="16" t="s">
+        <v>85</v>
+      </c>
+      <c r="L10" s="9" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="11" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B11" s="40"/>
+      <c r="C11" s="40"/>
+      <c r="D11" s="31" t="s">
+        <v>93</v>
+      </c>
+      <c r="E11" s="41" t="s">
+        <v>109</v>
+      </c>
+      <c r="G11" s="16" t="s">
         <v>143</v>
       </c>
-      <c r="H7" s="9" t="s">
+      <c r="H11" s="9" t="s">
+        <v>81</v>
+      </c>
+      <c r="K11" s="16" t="s">
+        <v>87</v>
+      </c>
+      <c r="L11" s="9" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="12" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B12" s="40"/>
+      <c r="C12" s="40"/>
+      <c r="D12" s="31" t="s">
+        <v>208</v>
+      </c>
+      <c r="E12" s="42" t="s">
+        <v>84</v>
+      </c>
+      <c r="G12" s="16" t="s">
+        <v>144</v>
+      </c>
+      <c r="H12" s="9" t="s">
+        <v>81</v>
+      </c>
+      <c r="K12" s="16" t="s">
+        <v>138</v>
+      </c>
+      <c r="L12" s="9" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="13" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B13" s="40"/>
+      <c r="C13" s="40"/>
+      <c r="D13" s="31" t="s">
+        <v>118</v>
+      </c>
+      <c r="E13" s="42" t="s">
+        <v>87</v>
+      </c>
+      <c r="G13" s="16" t="s">
+        <v>104</v>
+      </c>
+      <c r="H13" s="9" t="s">
+        <v>81</v>
+      </c>
+      <c r="K13" s="16" t="s">
+        <v>98</v>
+      </c>
+      <c r="L13" s="9" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="14" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B14" s="40"/>
+      <c r="C14" s="40"/>
+      <c r="D14" s="40"/>
+      <c r="E14" s="42" t="s">
+        <v>85</v>
+      </c>
+      <c r="G14" s="16" t="s">
+        <v>95</v>
+      </c>
+      <c r="H14" s="9" t="s">
+        <v>81</v>
+      </c>
+      <c r="K14" s="16" t="s">
+        <v>100</v>
+      </c>
+      <c r="L14" s="9" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="15" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B15" s="40"/>
+      <c r="C15" s="40"/>
+      <c r="D15" s="40"/>
+      <c r="E15" s="42" t="s">
+        <v>97</v>
+      </c>
+      <c r="G15" s="16" t="s">
+        <v>111</v>
+      </c>
+      <c r="H15" s="9" t="s">
+        <v>81</v>
+      </c>
+      <c r="K15" s="16" t="s">
+        <v>101</v>
+      </c>
+      <c r="L15" s="9" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="16" spans="2:12" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="B16" s="40"/>
+      <c r="C16" s="40"/>
+      <c r="D16" s="40"/>
+      <c r="E16" s="42" t="s">
+        <v>138</v>
+      </c>
+      <c r="G16" s="16" t="s">
+        <v>146</v>
+      </c>
+      <c r="H16" s="9" t="s">
+        <v>81</v>
+      </c>
+      <c r="K16" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="L16" s="9" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="17" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B17" s="40"/>
+      <c r="C17" s="40"/>
+      <c r="D17" s="40"/>
+      <c r="E17" s="42" t="s">
+        <v>96</v>
+      </c>
+      <c r="G17" s="16" t="s">
+        <v>90</v>
+      </c>
+      <c r="H17" s="9" t="s">
+        <v>81</v>
+      </c>
+      <c r="K17" s="16" t="s">
+        <v>103</v>
+      </c>
+      <c r="L17" s="9" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="18" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B18" s="40"/>
+      <c r="C18" s="40"/>
+      <c r="D18" s="40"/>
+      <c r="E18" s="41" t="s">
+        <v>138</v>
+      </c>
+      <c r="G18" s="16" t="s">
+        <v>145</v>
+      </c>
+      <c r="H18" s="9" t="s">
+        <v>81</v>
+      </c>
+      <c r="K18" s="16" t="s">
+        <v>166</v>
+      </c>
+      <c r="L18" s="9" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="19" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B19" s="40"/>
+      <c r="C19" s="40"/>
+      <c r="D19" s="40"/>
+      <c r="E19" s="42" t="s">
+        <v>85</v>
+      </c>
+      <c r="G19" s="16" t="s">
+        <v>99</v>
+      </c>
+      <c r="H19" s="9" t="s">
+        <v>81</v>
+      </c>
+      <c r="K19" s="16" t="s">
+        <v>108</v>
+      </c>
+      <c r="L19" s="9" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="20" spans="2:12" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="B20" s="40"/>
+      <c r="C20" s="40"/>
+      <c r="D20" s="40"/>
+      <c r="E20" s="42" t="s">
+        <v>100</v>
+      </c>
+      <c r="G20" s="16" t="s">
+        <v>147</v>
+      </c>
+      <c r="H20" s="9" t="s">
+        <v>81</v>
+      </c>
+      <c r="K20" s="16" t="s">
+        <v>89</v>
+      </c>
+      <c r="L20" s="9" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="21" spans="2:12" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="B21" s="40"/>
+      <c r="C21" s="40"/>
+      <c r="D21" s="40"/>
+      <c r="E21" s="41" t="s">
+        <v>84</v>
+      </c>
+      <c r="G21" s="16" t="s">
+        <v>148</v>
+      </c>
+      <c r="H21" s="9" t="s">
+        <v>81</v>
+      </c>
+      <c r="K21" s="16" t="s">
+        <v>92</v>
+      </c>
+      <c r="L21" s="9" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="22" spans="2:12" ht="56.25" x14ac:dyDescent="0.25">
+      <c r="B22" s="40"/>
+      <c r="C22" s="40"/>
+      <c r="D22" s="40"/>
+      <c r="E22" s="42" t="s">
+        <v>138</v>
+      </c>
+      <c r="G22" s="16" t="s">
+        <v>149</v>
+      </c>
+      <c r="H22" s="9" t="s">
+        <v>81</v>
+      </c>
+      <c r="K22" s="16" t="s">
+        <v>97</v>
+      </c>
+      <c r="L22" s="9" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="23" spans="2:12" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="B23" s="40"/>
+      <c r="C23" s="40"/>
+      <c r="D23" s="40"/>
+      <c r="E23" s="42" t="s">
+        <v>97</v>
+      </c>
+      <c r="G23" s="16" t="s">
+        <v>150</v>
+      </c>
+      <c r="H23" s="9" t="s">
+        <v>81</v>
+      </c>
+      <c r="K23" s="16" t="s">
         <v>83</v>
       </c>
-      <c r="K7" s="16" t="s">
-        <v>117</v>
-      </c>
-      <c r="L7" s="9" t="s">
+      <c r="L23" s="9" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="24" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B24" s="40"/>
+      <c r="C24" s="40"/>
+      <c r="D24" s="40"/>
+      <c r="E24" s="31" t="s">
+        <v>108</v>
+      </c>
+      <c r="G24" s="16" t="s">
+        <v>123</v>
+      </c>
+      <c r="H24" s="9" t="s">
+        <v>81</v>
+      </c>
+      <c r="K24" s="16" t="s">
+        <v>109</v>
+      </c>
+      <c r="L24" s="9" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="25" spans="2:12" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="E25" s="42" t="s">
+        <v>84</v>
+      </c>
+      <c r="G25" s="16" t="s">
+        <v>151</v>
+      </c>
+      <c r="H25" s="9" t="s">
+        <v>81</v>
+      </c>
+      <c r="K25" s="24" t="s">
+        <v>133</v>
+      </c>
+      <c r="L25" s="9" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="26" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="E26" s="42" t="s">
+        <v>87</v>
+      </c>
+      <c r="G26" s="16" t="s">
+        <v>167</v>
+      </c>
+      <c r="H26" s="9" t="s">
+        <v>81</v>
+      </c>
+      <c r="K26" s="24" t="s">
+        <v>132</v>
+      </c>
+      <c r="L26" s="9" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="27" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="E27" s="42" t="s">
+        <v>85</v>
+      </c>
+      <c r="G27" s="23" t="s">
+        <v>86</v>
+      </c>
+      <c r="H27" s="9" t="s">
+        <v>81</v>
+      </c>
+      <c r="K27" s="23" t="s">
+        <v>82</v>
+      </c>
+      <c r="L27" s="9" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="28" spans="2:12" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="E28" s="42" t="s">
+        <v>89</v>
+      </c>
+      <c r="G28" s="23" t="s">
+        <v>154</v>
+      </c>
+      <c r="H28" s="9" t="s">
+        <v>81</v>
+      </c>
+      <c r="K28" s="23" t="s">
+        <v>107</v>
+      </c>
+      <c r="L28" s="9" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="29" spans="2:12" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="E29" s="31" t="s">
         <v>83</v>
       </c>
-    </row>
-    <row r="8" spans="2:12" ht="37.5" x14ac:dyDescent="0.25">
-      <c r="B8" s="34"/>
-      <c r="C8" s="34"/>
-      <c r="D8" s="33"/>
-      <c r="G8" s="16" t="s">
-        <v>144</v>
-      </c>
-      <c r="H8" s="9" t="s">
-        <v>83</v>
-      </c>
-      <c r="K8" s="16" t="s">
+      <c r="G29" s="23" t="s">
+        <v>155</v>
+      </c>
+      <c r="H29" s="9" t="s">
+        <v>81</v>
+      </c>
+      <c r="K29" s="23" t="s">
+        <v>168</v>
+      </c>
+      <c r="L29" s="9" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="30" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="E30" s="41" t="s">
+        <v>84</v>
+      </c>
+      <c r="G30" s="23" t="s">
+        <v>112</v>
+      </c>
+      <c r="H30" s="9" t="s">
+        <v>81</v>
+      </c>
+      <c r="K30" s="23" t="s">
+        <v>113</v>
+      </c>
+      <c r="L30" s="9" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="31" spans="2:12" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="E31" s="42" t="s">
+        <v>87</v>
+      </c>
+      <c r="G31" s="23" t="s">
+        <v>156</v>
+      </c>
+      <c r="H31" s="9" t="s">
+        <v>81</v>
+      </c>
+      <c r="K31" s="23" t="s">
+        <v>96</v>
+      </c>
+      <c r="L31" s="9" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="32" spans="2:12" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="E32" s="42" t="s">
+        <v>85</v>
+      </c>
+      <c r="G32" s="23" t="s">
+        <v>152</v>
+      </c>
+      <c r="H32" s="9" t="s">
+        <v>153</v>
+      </c>
+      <c r="K32" s="23" t="s">
+        <v>135</v>
+      </c>
+      <c r="L32" s="9" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="33" spans="5:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="E33" s="41" t="s">
+        <v>84</v>
+      </c>
+      <c r="G33" s="24" t="s">
+        <v>157</v>
+      </c>
+      <c r="H33" s="9" t="s">
+        <v>81</v>
+      </c>
+      <c r="K33" s="25" t="s">
+        <v>169</v>
+      </c>
+      <c r="L33" s="19" t="s">
         <v>139</v>
       </c>
-      <c r="L8" s="9" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="9" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B9" s="32"/>
-      <c r="C9" s="32"/>
-      <c r="D9" s="33"/>
-      <c r="G9" s="16" t="s">
-        <v>108</v>
-      </c>
-      <c r="H9" s="9" t="s">
-        <v>83</v>
-      </c>
-      <c r="K9" s="16" t="s">
-        <v>86</v>
-      </c>
-      <c r="L9" s="9" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="10" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B10" s="32"/>
-      <c r="C10" s="32"/>
-      <c r="D10" s="33"/>
-      <c r="G10" s="16" t="s">
-        <v>90</v>
-      </c>
-      <c r="H10" s="9" t="s">
-        <v>83</v>
-      </c>
-      <c r="K10" s="16" t="s">
+    </row>
+    <row r="34" spans="5:12" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="E34" s="42" t="s">
         <v>87</v>
       </c>
-      <c r="L10" s="9" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="11" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B11" s="34"/>
-      <c r="C11" s="34"/>
-      <c r="D11" s="33"/>
-      <c r="G11" s="16" t="s">
-        <v>145</v>
-      </c>
-      <c r="H11" s="9" t="s">
-        <v>83</v>
-      </c>
-      <c r="K11" s="16" t="s">
-        <v>89</v>
-      </c>
-      <c r="L11" s="9" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="12" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B12" s="32"/>
-      <c r="C12" s="32"/>
-      <c r="D12" s="33"/>
-      <c r="G12" s="16" t="s">
-        <v>146</v>
-      </c>
-      <c r="H12" s="9" t="s">
-        <v>83</v>
-      </c>
-      <c r="K12" s="16" t="s">
-        <v>140</v>
-      </c>
-      <c r="L12" s="9" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="13" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B13" s="32"/>
-      <c r="C13" s="32"/>
-      <c r="D13" s="33"/>
-      <c r="G13" s="16" t="s">
-        <v>106</v>
-      </c>
-      <c r="H13" s="9" t="s">
-        <v>83</v>
-      </c>
-      <c r="K13" s="16" t="s">
-        <v>100</v>
-      </c>
-      <c r="L13" s="9" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="14" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B14" s="34"/>
-      <c r="C14" s="34"/>
-      <c r="D14" s="33"/>
-      <c r="G14" s="16" t="s">
-        <v>97</v>
-      </c>
-      <c r="H14" s="9" t="s">
-        <v>83</v>
-      </c>
-      <c r="K14" s="16" t="s">
-        <v>102</v>
-      </c>
-      <c r="L14" s="9" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="15" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B15" s="32"/>
-      <c r="C15" s="32"/>
-      <c r="D15" s="33"/>
-      <c r="G15" s="16" t="s">
-        <v>113</v>
-      </c>
-      <c r="H15" s="9" t="s">
-        <v>83</v>
-      </c>
-      <c r="K15" s="16" t="s">
-        <v>103</v>
-      </c>
-      <c r="L15" s="9" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="16" spans="2:12" ht="37.5" x14ac:dyDescent="0.25">
-      <c r="B16" s="32"/>
-      <c r="C16" s="32"/>
-      <c r="D16" s="33"/>
-      <c r="G16" s="16" t="s">
-        <v>148</v>
-      </c>
-      <c r="H16" s="9" t="s">
-        <v>83</v>
-      </c>
-      <c r="K16" s="16" t="s">
-        <v>96</v>
-      </c>
-      <c r="L16" s="9" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="17" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G17" s="16" t="s">
-        <v>92</v>
-      </c>
-      <c r="H17" s="9" t="s">
-        <v>83</v>
-      </c>
-      <c r="K17" s="16" t="s">
-        <v>105</v>
-      </c>
-      <c r="L17" s="9" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="18" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G18" s="16" t="s">
-        <v>147</v>
-      </c>
-      <c r="H18" s="9" t="s">
-        <v>83</v>
-      </c>
-      <c r="K18" s="16" t="s">
-        <v>168</v>
-      </c>
-      <c r="L18" s="9" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="19" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G19" s="16" t="s">
-        <v>101</v>
-      </c>
-      <c r="H19" s="9" t="s">
-        <v>83</v>
-      </c>
-      <c r="K19" s="16" t="s">
-        <v>110</v>
-      </c>
-      <c r="L19" s="9" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="20" spans="7:12" ht="37.5" x14ac:dyDescent="0.25">
-      <c r="G20" s="16" t="s">
-        <v>149</v>
-      </c>
-      <c r="H20" s="9" t="s">
-        <v>83</v>
-      </c>
-      <c r="K20" s="16" t="s">
-        <v>91</v>
-      </c>
-      <c r="L20" s="9" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="21" spans="7:12" ht="37.5" x14ac:dyDescent="0.25">
-      <c r="G21" s="16" t="s">
-        <v>150</v>
-      </c>
-      <c r="H21" s="9" t="s">
-        <v>83</v>
-      </c>
-      <c r="K21" s="16" t="s">
-        <v>94</v>
-      </c>
-      <c r="L21" s="9" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="22" spans="7:12" ht="56.25" x14ac:dyDescent="0.25">
-      <c r="G22" s="16" t="s">
-        <v>151</v>
-      </c>
-      <c r="H22" s="9" t="s">
-        <v>83</v>
-      </c>
-      <c r="K22" s="16" t="s">
-        <v>99</v>
-      </c>
-      <c r="L22" s="9" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="23" spans="7:12" ht="37.5" x14ac:dyDescent="0.25">
-      <c r="G23" s="16" t="s">
-        <v>152</v>
-      </c>
-      <c r="H23" s="9" t="s">
-        <v>83</v>
-      </c>
-      <c r="K23" s="16" t="s">
-        <v>85</v>
-      </c>
-      <c r="L23" s="9" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="24" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G24" s="16" t="s">
-        <v>125</v>
-      </c>
-      <c r="H24" s="9" t="s">
-        <v>83</v>
-      </c>
-      <c r="K24" s="16" t="s">
-        <v>111</v>
-      </c>
-      <c r="L24" s="9" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="25" spans="7:12" ht="37.5" x14ac:dyDescent="0.25">
-      <c r="G25" s="16" t="s">
-        <v>153</v>
-      </c>
-      <c r="H25" s="9" t="s">
-        <v>83</v>
-      </c>
-      <c r="K25" s="24" t="s">
-        <v>135</v>
-      </c>
-      <c r="L25" s="9" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="26" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G26" s="16" t="s">
-        <v>169</v>
-      </c>
-      <c r="H26" s="9" t="s">
-        <v>83</v>
-      </c>
-      <c r="K26" s="24" t="s">
-        <v>134</v>
-      </c>
-      <c r="L26" s="9" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="27" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G27" s="23" t="s">
-        <v>88</v>
-      </c>
-      <c r="H27" s="9" t="s">
-        <v>83</v>
-      </c>
-      <c r="K27" s="23" t="s">
-        <v>84</v>
-      </c>
-      <c r="L27" s="9" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="28" spans="7:12" ht="37.5" x14ac:dyDescent="0.25">
-      <c r="G28" s="23" t="s">
-        <v>156</v>
-      </c>
-      <c r="H28" s="9" t="s">
-        <v>83</v>
-      </c>
-      <c r="K28" s="23" t="s">
-        <v>109</v>
-      </c>
-      <c r="L28" s="9" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="29" spans="7:12" ht="37.5" x14ac:dyDescent="0.25">
-      <c r="G29" s="23" t="s">
-        <v>157</v>
-      </c>
-      <c r="H29" s="9" t="s">
-        <v>83</v>
-      </c>
-      <c r="K29" s="23" t="s">
-        <v>170</v>
-      </c>
-      <c r="L29" s="9" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="30" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G30" s="23" t="s">
-        <v>114</v>
-      </c>
-      <c r="H30" s="9" t="s">
-        <v>83</v>
-      </c>
-      <c r="K30" s="23" t="s">
-        <v>115</v>
-      </c>
-      <c r="L30" s="9" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="31" spans="7:12" ht="37.5" x14ac:dyDescent="0.25">
-      <c r="G31" s="23" t="s">
+      <c r="G34" s="24" t="s">
         <v>158</v>
       </c>
-      <c r="H31" s="9" t="s">
-        <v>83</v>
-      </c>
-      <c r="K31" s="23" t="s">
-        <v>98</v>
-      </c>
-      <c r="L31" s="9" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="32" spans="7:12" ht="37.5" x14ac:dyDescent="0.25">
-      <c r="G32" s="23" t="s">
-        <v>154</v>
-      </c>
-      <c r="H32" s="9" t="s">
-        <v>155</v>
-      </c>
-      <c r="K32" s="23" t="s">
-        <v>137</v>
-      </c>
-      <c r="L32" s="9" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="33" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G33" s="24" t="s">
-        <v>159</v>
-      </c>
-      <c r="H33" s="9" t="s">
-        <v>83</v>
-      </c>
-      <c r="K33" s="25" t="s">
-        <v>171</v>
-      </c>
-      <c r="L33" s="19" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="34" spans="7:12" ht="37.5" x14ac:dyDescent="0.25">
-      <c r="G34" s="24" t="s">
-        <v>160</v>
-      </c>
       <c r="H34" s="9" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="K34" s="15"/>
       <c r="L34" s="15"/>
     </row>
-    <row r="35" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="35" spans="5:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="E35" s="42" t="s">
+        <v>85</v>
+      </c>
       <c r="G35" s="24" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="H35" s="9" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="K35" s="20"/>
       <c r="L35" s="20"/>
     </row>
-    <row r="36" spans="7:12" ht="37.5" x14ac:dyDescent="0.25">
+    <row r="36" spans="5:12" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="E36" s="42" t="s">
+        <v>89</v>
+      </c>
       <c r="G36" s="24" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="H36" s="9" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="K36" s="20"/>
       <c r="L36" s="20"/>
     </row>
-    <row r="37" spans="7:12" ht="37.5" x14ac:dyDescent="0.25">
+    <row r="37" spans="5:12" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="E37" s="42" t="s">
+        <v>83</v>
+      </c>
       <c r="G37" s="9" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="H37" s="9" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="K37" s="20"/>
       <c r="L37" s="20"/>
     </row>
-    <row r="38" spans="7:12" ht="37.5" x14ac:dyDescent="0.25">
+    <row r="38" spans="5:12" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="E38" s="44" t="s">
+        <v>138</v>
+      </c>
       <c r="G38" s="9" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="H38" s="9" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="K38" s="20"/>
       <c r="L38" s="20"/>
     </row>
-    <row r="39" spans="7:12" ht="37.5" x14ac:dyDescent="0.25">
+    <row r="39" spans="5:12" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="E39" s="45" t="s">
+        <v>108</v>
+      </c>
       <c r="G39" s="9" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="H39" s="9" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="K39" s="20"/>
       <c r="L39" s="20"/>
     </row>
-    <row r="40" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="40" spans="5:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="E40" s="47" t="s">
+        <v>108</v>
+      </c>
       <c r="G40" s="20"/>
       <c r="H40" s="20"/>
       <c r="K40" s="20"/>
       <c r="L40" s="20"/>
     </row>
-    <row r="41" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="41" spans="5:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="E41" s="41" t="s">
+        <v>84</v>
+      </c>
       <c r="G41" s="20"/>
       <c r="H41" s="20"/>
       <c r="K41" s="20"/>
       <c r="L41" s="20"/>
     </row>
-    <row r="42" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="42" spans="5:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="E42" s="42" t="s">
+        <v>87</v>
+      </c>
       <c r="G42" s="20"/>
       <c r="H42" s="20"/>
       <c r="K42" s="20"/>
       <c r="L42" s="20"/>
     </row>
-    <row r="43" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="43" spans="5:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="E43" s="42" t="s">
+        <v>85</v>
+      </c>
       <c r="G43" s="20"/>
       <c r="H43" s="20"/>
       <c r="K43" s="20"/>
       <c r="L43" s="20"/>
     </row>
-    <row r="44" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="44" spans="5:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="E44" s="42" t="s">
+        <v>89</v>
+      </c>
       <c r="G44" s="20"/>
       <c r="H44" s="20"/>
       <c r="K44" s="20"/>
       <c r="L44" s="20"/>
     </row>
-    <row r="45" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="45" spans="5:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="E45" s="42" t="s">
+        <v>83</v>
+      </c>
       <c r="G45" s="20"/>
       <c r="H45" s="20"/>
       <c r="K45" s="20"/>
       <c r="L45" s="20"/>
     </row>
-    <row r="46" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="46" spans="5:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="E46" s="44" t="s">
+        <v>98</v>
+      </c>
       <c r="G46" s="20"/>
       <c r="H46" s="20"/>
       <c r="K46" s="20"/>
       <c r="L46" s="20"/>
     </row>
-    <row r="47" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="47" spans="5:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="E47" s="47" t="s">
+        <v>85</v>
+      </c>
       <c r="G47" s="20"/>
       <c r="H47" s="20"/>
       <c r="K47" s="20"/>
       <c r="L47" s="20"/>
     </row>
-    <row r="48" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="48" spans="5:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="E48" s="44" t="s">
+        <v>84</v>
+      </c>
       <c r="G48" s="20"/>
       <c r="H48" s="20"/>
       <c r="K48" s="20"/>
       <c r="L48" s="20"/>
     </row>
-    <row r="49" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="49" spans="5:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="E49" s="44" t="s">
+        <v>98</v>
+      </c>
       <c r="G49" s="20"/>
       <c r="H49" s="20"/>
       <c r="K49" s="20"/>
       <c r="L49" s="20"/>
     </row>
-    <row r="50" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="50" spans="5:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="E50" s="45" t="s">
+        <v>97</v>
+      </c>
       <c r="G50" s="20"/>
       <c r="H50" s="20"/>
       <c r="K50" s="20"/>
       <c r="L50" s="20"/>
     </row>
-    <row r="51" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="51" spans="5:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="E51" s="47" t="s">
+        <v>97</v>
+      </c>
       <c r="G51" s="20"/>
       <c r="H51" s="20"/>
       <c r="K51" s="20"/>
       <c r="L51" s="20"/>
     </row>
-    <row r="52" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="52" spans="5:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="E52" s="44" t="s">
+        <v>98</v>
+      </c>
       <c r="G52" s="20"/>
       <c r="H52" s="20"/>
       <c r="K52" s="20"/>
       <c r="L52" s="20"/>
+    </row>
+    <row r="53" spans="5:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="E53" s="45" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="54" spans="5:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="E54" s="44" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="55" spans="5:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="E55" s="44" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="56" spans="5:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="E56" s="45" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="57" spans="5:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="E57" s="44" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="58" spans="5:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="E58" s="44" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="59" spans="5:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="E59" s="48"/>
+    </row>
+    <row r="60" spans="5:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="E60" s="46"/>
+    </row>
+    <row r="61" spans="5:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="E61" s="46"/>
+    </row>
+    <row r="62" spans="5:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="E62" s="46"/>
+    </row>
+    <row r="63" spans="5:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="E63" s="46"/>
+    </row>
+    <row r="64" spans="5:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="E64" s="46"/>
+    </row>
+    <row r="65" spans="5:5" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="E65" s="46"/>
+    </row>
+    <row r="66" spans="5:5" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="E66" s="46"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -7164,93 +7603,94 @@
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="4" width="22.5703125" customWidth="1"/>
+    <col min="5" max="5" width="22.85546875" customWidth="1"/>
     <col min="7" max="8" width="22.5703125" customWidth="1"/>
     <col min="11" max="12" width="22.5703125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="2" spans="2:12" ht="47.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="35" t="s">
-        <v>230</v>
-      </c>
-      <c r="C2" s="36"/>
-      <c r="D2" s="37"/>
+      <c r="B2" s="34" t="s">
+        <v>227</v>
+      </c>
+      <c r="C2" s="35"/>
+      <c r="D2" s="36"/>
       <c r="G2" s="2" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="H2" s="2" t="s">
         <v>15</v>
       </c>
       <c r="K2" s="2" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="L2" s="2" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="3" spans="2:12" ht="24" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B3" s="38" t="s">
-        <v>231</v>
-      </c>
-      <c r="C3" s="39"/>
-      <c r="D3" s="40"/>
+      <c r="B3" s="37" t="s">
+        <v>228</v>
+      </c>
+      <c r="C3" s="38"/>
+      <c r="D3" s="39"/>
       <c r="G3" s="6" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="H3" s="6" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="K3" s="28" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="L3" s="6" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
     </row>
     <row r="4" spans="2:12" ht="24" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B4" s="2" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>234</v>
+        <v>231</v>
       </c>
       <c r="G4" s="9" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="H4" s="9" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="K4" s="26" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="L4" s="9" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
     </row>
     <row r="5" spans="2:12" ht="56.25" x14ac:dyDescent="0.25">
       <c r="B5" s="31" t="s">
-        <v>242</v>
+        <v>239</v>
       </c>
       <c r="C5" s="31" t="s">
-        <v>235</v>
+        <v>232</v>
       </c>
       <c r="D5" s="31" t="s">
-        <v>243</v>
+        <v>240</v>
       </c>
       <c r="G5" s="9" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="H5" s="9" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="K5" s="26" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="L5" s="9" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
     </row>
     <row r="6" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
@@ -7258,526 +7698,605 @@
       <c r="C6" s="32"/>
       <c r="D6" s="33"/>
       <c r="G6" s="26" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="H6" s="9" t="s">
+        <v>81</v>
+      </c>
+      <c r="K6" s="26" t="s">
         <v>83</v>
       </c>
-      <c r="K6" s="26" t="s">
-        <v>85</v>
-      </c>
       <c r="L6" s="9" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="7" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="7" spans="2:12" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B7" s="32"/>
       <c r="C7" s="32"/>
       <c r="D7" s="33"/>
       <c r="G7" s="26" t="s">
+        <v>173</v>
+      </c>
+      <c r="H7" s="9" t="s">
+        <v>81</v>
+      </c>
+      <c r="K7" s="26" t="s">
+        <v>89</v>
+      </c>
+      <c r="L7" s="9" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="8" spans="2:12" ht="47.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B8" s="2" t="s">
+        <v>244</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>245</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>246</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>247</v>
+      </c>
+      <c r="G8" s="17" t="s">
+        <v>174</v>
+      </c>
+      <c r="H8" s="9" t="s">
+        <v>81</v>
+      </c>
+      <c r="K8" s="17" t="s">
+        <v>109</v>
+      </c>
+      <c r="L8" s="9" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="9" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B9" s="31" t="s">
+        <v>248</v>
+      </c>
+      <c r="C9" s="40"/>
+      <c r="D9" s="31" t="s">
+        <v>174</v>
+      </c>
+      <c r="E9" s="42" t="s">
+        <v>96</v>
+      </c>
+      <c r="G9" s="17" t="s">
         <v>175</v>
       </c>
-      <c r="H7" s="9" t="s">
+      <c r="H9" s="9" t="s">
+        <v>81</v>
+      </c>
+      <c r="K9" s="17" t="s">
+        <v>103</v>
+      </c>
+      <c r="L9" s="9" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="10" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B10" s="31" t="s">
+        <v>157</v>
+      </c>
+      <c r="C10" s="40"/>
+      <c r="D10" s="31" t="s">
+        <v>104</v>
+      </c>
+      <c r="E10" s="42" t="s">
+        <v>97</v>
+      </c>
+      <c r="G10" s="17" t="s">
+        <v>176</v>
+      </c>
+      <c r="H10" s="9" t="s">
+        <v>196</v>
+      </c>
+      <c r="K10" s="17" t="s">
+        <v>200</v>
+      </c>
+      <c r="L10" s="9" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="11" spans="2:12" ht="56.25" x14ac:dyDescent="0.25">
+      <c r="B11" s="31" t="s">
+        <v>119</v>
+      </c>
+      <c r="C11" s="40"/>
+      <c r="D11" s="43" t="s">
+        <v>209</v>
+      </c>
+      <c r="E11" s="42" t="s">
+        <v>98</v>
+      </c>
+      <c r="G11" s="17" t="s">
+        <v>180</v>
+      </c>
+      <c r="H11" s="9" t="s">
+        <v>196</v>
+      </c>
+      <c r="K11" s="17" t="s">
+        <v>105</v>
+      </c>
+      <c r="L11" s="9" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="12" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B12" s="31" t="s">
+        <v>118</v>
+      </c>
+      <c r="C12" s="40"/>
+      <c r="D12" s="40"/>
+      <c r="E12" s="42" t="s">
+        <v>84</v>
+      </c>
+      <c r="G12" s="17" t="s">
+        <v>177</v>
+      </c>
+      <c r="H12" s="9" t="s">
+        <v>81</v>
+      </c>
+      <c r="K12" s="17" t="s">
+        <v>94</v>
+      </c>
+      <c r="L12" s="9" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="13" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B13" s="31" t="s">
+        <v>254</v>
+      </c>
+      <c r="C13" s="40"/>
+      <c r="D13" s="40"/>
+      <c r="E13" s="42" t="s">
+        <v>109</v>
+      </c>
+      <c r="G13" s="17" t="s">
+        <v>178</v>
+      </c>
+      <c r="H13" s="9" t="s">
+        <v>81</v>
+      </c>
+      <c r="K13" s="17" t="s">
+        <v>92</v>
+      </c>
+      <c r="L13" s="9" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="14" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B14" s="40"/>
+      <c r="C14" s="40"/>
+      <c r="D14" s="40"/>
+      <c r="E14" s="31" t="s">
         <v>83</v>
       </c>
-      <c r="K7" s="26" t="s">
-        <v>91</v>
-      </c>
-      <c r="L7" s="9" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="8" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B8" s="34"/>
-      <c r="C8" s="34"/>
-      <c r="D8" s="33"/>
-      <c r="G8" s="17" t="s">
-        <v>176</v>
-      </c>
-      <c r="H8" s="9" t="s">
-        <v>83</v>
-      </c>
-      <c r="K8" s="17" t="s">
-        <v>111</v>
-      </c>
-      <c r="L8" s="9" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="9" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B9" s="32"/>
-      <c r="C9" s="32"/>
-      <c r="D9" s="33"/>
-      <c r="G9" s="17" t="s">
-        <v>177</v>
-      </c>
-      <c r="H9" s="9" t="s">
-        <v>83</v>
-      </c>
-      <c r="K9" s="17" t="s">
-        <v>105</v>
-      </c>
-      <c r="L9" s="9" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="10" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B10" s="32"/>
-      <c r="C10" s="32"/>
-      <c r="D10" s="33"/>
-      <c r="G10" s="17" t="s">
-        <v>178</v>
-      </c>
-      <c r="H10" s="9" t="s">
+      <c r="G14" s="17" t="s">
+        <v>179</v>
+      </c>
+      <c r="H14" s="9" t="s">
+        <v>81</v>
+      </c>
+      <c r="K14" s="17" t="s">
+        <v>85</v>
+      </c>
+      <c r="L14" s="9" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="15" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B15" s="40"/>
+      <c r="C15" s="40"/>
+      <c r="D15" s="40"/>
+      <c r="E15" s="43" t="s">
+        <v>98</v>
+      </c>
+      <c r="G15" s="17" t="s">
+        <v>104</v>
+      </c>
+      <c r="H15" s="9" t="s">
+        <v>81</v>
+      </c>
+      <c r="K15" s="17" t="s">
+        <v>87</v>
+      </c>
+      <c r="L15" s="9" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="16" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B16" s="40"/>
+      <c r="C16" s="40"/>
+      <c r="D16" s="40"/>
+      <c r="E16" s="40"/>
+      <c r="G16" s="14" t="s">
+        <v>93</v>
+      </c>
+      <c r="H16" s="9" t="s">
+        <v>81</v>
+      </c>
+      <c r="K16" s="17" t="s">
+        <v>107</v>
+      </c>
+      <c r="L16" s="9" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="17" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B17" s="40"/>
+      <c r="C17" s="40"/>
+      <c r="D17" s="40"/>
+      <c r="E17" s="40"/>
+      <c r="G17" s="14" t="s">
+        <v>141</v>
+      </c>
+      <c r="H17" s="9" t="s">
+        <v>81</v>
+      </c>
+      <c r="K17" s="17" t="s">
+        <v>97</v>
+      </c>
+      <c r="L17" s="9" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="18" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B18" s="40"/>
+      <c r="C18" s="40"/>
+      <c r="D18" s="40"/>
+      <c r="E18" s="40"/>
+      <c r="G18" s="14" t="s">
+        <v>159</v>
+      </c>
+      <c r="H18" s="9" t="s">
+        <v>81</v>
+      </c>
+      <c r="K18" s="17" t="s">
+        <v>138</v>
+      </c>
+      <c r="L18" s="9" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="19" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B19" s="40"/>
+      <c r="C19" s="40"/>
+      <c r="D19" s="40"/>
+      <c r="E19" s="40"/>
+      <c r="G19" s="14" t="s">
+        <v>181</v>
+      </c>
+      <c r="H19" s="9" t="s">
+        <v>81</v>
+      </c>
+      <c r="K19" s="17" t="s">
+        <v>98</v>
+      </c>
+      <c r="L19" s="9" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="20" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B20" s="40"/>
+      <c r="C20" s="40"/>
+      <c r="D20" s="40"/>
+      <c r="E20" s="40"/>
+      <c r="G20" s="14" t="s">
+        <v>123</v>
+      </c>
+      <c r="H20" s="9" t="s">
+        <v>81</v>
+      </c>
+      <c r="K20" s="17" t="s">
+        <v>108</v>
+      </c>
+      <c r="L20" s="9" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="21" spans="2:12" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="B21" s="40"/>
+      <c r="C21" s="40"/>
+      <c r="D21" s="40"/>
+      <c r="E21" s="40"/>
+      <c r="G21" s="14" t="s">
+        <v>182</v>
+      </c>
+      <c r="H21" s="9" t="s">
+        <v>81</v>
+      </c>
+      <c r="K21" s="17" t="s">
+        <v>114</v>
+      </c>
+      <c r="L21" s="9" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="22" spans="2:12" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="B22" s="40"/>
+      <c r="C22" s="40"/>
+      <c r="D22" s="40"/>
+      <c r="E22" s="40"/>
+      <c r="G22" s="14" t="s">
+        <v>183</v>
+      </c>
+      <c r="H22" s="9" t="s">
+        <v>81</v>
+      </c>
+      <c r="K22" s="17" t="s">
+        <v>115</v>
+      </c>
+      <c r="L22" s="9" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="23" spans="2:12" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="B23" s="40"/>
+      <c r="C23" s="40"/>
+      <c r="D23" s="40"/>
+      <c r="E23" s="40"/>
+      <c r="G23" s="14" t="s">
+        <v>184</v>
+      </c>
+      <c r="H23" s="9" t="s">
+        <v>81</v>
+      </c>
+      <c r="K23" s="14" t="s">
+        <v>197</v>
+      </c>
+      <c r="L23" s="9" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="24" spans="2:12" ht="56.25" x14ac:dyDescent="0.25">
+      <c r="B24" s="40"/>
+      <c r="C24" s="40"/>
+      <c r="D24" s="40"/>
+      <c r="E24" s="40"/>
+      <c r="G24" s="14" t="s">
+        <v>185</v>
+      </c>
+      <c r="H24" s="9" t="s">
+        <v>81</v>
+      </c>
+      <c r="K24" s="14" t="s">
         <v>198</v>
       </c>
-      <c r="K10" s="17" t="s">
-        <v>202</v>
-      </c>
-      <c r="L10" s="9" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="11" spans="2:12" ht="56.25" x14ac:dyDescent="0.25">
-      <c r="B11" s="34"/>
-      <c r="C11" s="34"/>
-      <c r="D11" s="33"/>
-      <c r="G11" s="17" t="s">
-        <v>182</v>
-      </c>
-      <c r="H11" s="9" t="s">
-        <v>198</v>
-      </c>
-      <c r="K11" s="17" t="s">
-        <v>107</v>
-      </c>
-      <c r="L11" s="9" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="12" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B12" s="32"/>
-      <c r="C12" s="32"/>
-      <c r="D12" s="33"/>
-      <c r="G12" s="17" t="s">
-        <v>179</v>
-      </c>
-      <c r="H12" s="9" t="s">
-        <v>83</v>
-      </c>
-      <c r="K12" s="17" t="s">
+      <c r="L24" s="9" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="25" spans="2:12" ht="56.25" x14ac:dyDescent="0.25">
+      <c r="G25" s="14" t="s">
+        <v>186</v>
+      </c>
+      <c r="H25" s="9" t="s">
+        <v>81</v>
+      </c>
+      <c r="K25" s="14" t="s">
         <v>96</v>
       </c>
-      <c r="L12" s="9" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="13" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B13" s="32"/>
-      <c r="C13" s="32"/>
-      <c r="D13" s="33"/>
-      <c r="G13" s="17" t="s">
-        <v>180</v>
-      </c>
-      <c r="H13" s="9" t="s">
-        <v>83</v>
-      </c>
-      <c r="K13" s="17" t="s">
-        <v>94</v>
-      </c>
-      <c r="L13" s="9" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="14" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B14" s="34"/>
-      <c r="C14" s="34"/>
-      <c r="D14" s="33"/>
-      <c r="G14" s="17" t="s">
-        <v>181</v>
-      </c>
-      <c r="H14" s="9" t="s">
-        <v>83</v>
-      </c>
-      <c r="K14" s="17" t="s">
-        <v>87</v>
-      </c>
-      <c r="L14" s="9" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="15" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B15" s="32"/>
-      <c r="C15" s="32"/>
-      <c r="D15" s="33"/>
-      <c r="G15" s="17" t="s">
-        <v>106</v>
-      </c>
-      <c r="H15" s="9" t="s">
-        <v>83</v>
-      </c>
-      <c r="K15" s="17" t="s">
-        <v>89</v>
-      </c>
-      <c r="L15" s="9" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="16" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B16" s="32"/>
-      <c r="C16" s="32"/>
-      <c r="D16" s="33"/>
-      <c r="G16" s="14" t="s">
-        <v>95</v>
-      </c>
-      <c r="H16" s="9" t="s">
-        <v>83</v>
-      </c>
-      <c r="K16" s="17" t="s">
-        <v>109</v>
-      </c>
-      <c r="L16" s="9" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="17" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G17" s="14" t="s">
-        <v>143</v>
-      </c>
-      <c r="H17" s="9" t="s">
-        <v>83</v>
-      </c>
-      <c r="K17" s="17" t="s">
-        <v>99</v>
-      </c>
-      <c r="L17" s="9" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="18" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G18" s="14" t="s">
-        <v>161</v>
-      </c>
-      <c r="H18" s="9" t="s">
-        <v>83</v>
-      </c>
-      <c r="K18" s="17" t="s">
+      <c r="L25" s="9" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="26" spans="2:12" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="G26" s="14" t="s">
+        <v>189</v>
+      </c>
+      <c r="H26" s="9" t="s">
+        <v>81</v>
+      </c>
+      <c r="K26" s="14" t="s">
+        <v>101</v>
+      </c>
+      <c r="L26" s="9" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="27" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G27" s="24" t="s">
+        <v>90</v>
+      </c>
+      <c r="H27" s="9" t="s">
+        <v>81</v>
+      </c>
+      <c r="K27" s="14" t="s">
+        <v>100</v>
+      </c>
+      <c r="L27" s="9" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="28" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G28" s="24" t="s">
         <v>140</v>
       </c>
-      <c r="L18" s="9" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="19" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G19" s="14" t="s">
-        <v>183</v>
-      </c>
-      <c r="H19" s="9" t="s">
-        <v>83</v>
-      </c>
-      <c r="K19" s="17" t="s">
-        <v>100</v>
-      </c>
-      <c r="L19" s="9" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="20" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G20" s="14" t="s">
-        <v>125</v>
-      </c>
-      <c r="H20" s="9" t="s">
-        <v>83</v>
-      </c>
-      <c r="K20" s="17" t="s">
-        <v>110</v>
-      </c>
-      <c r="L20" s="9" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="21" spans="7:12" ht="37.5" x14ac:dyDescent="0.25">
-      <c r="G21" s="14" t="s">
-        <v>184</v>
-      </c>
-      <c r="H21" s="9" t="s">
-        <v>83</v>
-      </c>
-      <c r="K21" s="17" t="s">
-        <v>116</v>
-      </c>
-      <c r="L21" s="9" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="22" spans="7:12" ht="37.5" x14ac:dyDescent="0.25">
-      <c r="G22" s="14" t="s">
-        <v>185</v>
-      </c>
-      <c r="H22" s="9" t="s">
-        <v>83</v>
-      </c>
-      <c r="K22" s="17" t="s">
-        <v>117</v>
-      </c>
-      <c r="L22" s="9" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="23" spans="7:12" ht="37.5" x14ac:dyDescent="0.25">
-      <c r="G23" s="14" t="s">
-        <v>186</v>
-      </c>
-      <c r="H23" s="9" t="s">
-        <v>83</v>
-      </c>
-      <c r="K23" s="14" t="s">
+      <c r="H28" s="9" t="s">
+        <v>81</v>
+      </c>
+      <c r="K28" s="14" t="s">
+        <v>113</v>
+      </c>
+      <c r="L28" s="9" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="29" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G29" s="24" t="s">
+        <v>88</v>
+      </c>
+      <c r="H29" s="9" t="s">
+        <v>81</v>
+      </c>
+      <c r="K29" s="14" t="s">
+        <v>133</v>
+      </c>
+      <c r="L29" s="9" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="30" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G30" s="24" t="s">
+        <v>119</v>
+      </c>
+      <c r="H30" s="9" t="s">
+        <v>81</v>
+      </c>
+      <c r="K30" s="14" t="s">
+        <v>132</v>
+      </c>
+      <c r="L30" s="9" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="31" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G31" s="24" t="s">
+        <v>145</v>
+      </c>
+      <c r="H31" s="9" t="s">
+        <v>81</v>
+      </c>
+      <c r="K31" s="16" t="s">
+        <v>84</v>
+      </c>
+      <c r="L31" s="9" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="32" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G32" s="24" t="s">
+        <v>187</v>
+      </c>
+      <c r="H32" s="9" t="s">
+        <v>81</v>
+      </c>
+      <c r="K32" s="16" t="s">
         <v>199</v>
       </c>
-      <c r="L23" s="9" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="24" spans="7:12" ht="56.25" x14ac:dyDescent="0.25">
-      <c r="G24" s="14" t="s">
-        <v>187</v>
-      </c>
-      <c r="H24" s="9" t="s">
-        <v>83</v>
-      </c>
-      <c r="K24" s="14" t="s">
-        <v>200</v>
-      </c>
-      <c r="L24" s="9" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="25" spans="7:12" ht="56.25" x14ac:dyDescent="0.25">
-      <c r="G25" s="14" t="s">
-        <v>188</v>
-      </c>
-      <c r="H25" s="9" t="s">
-        <v>83</v>
-      </c>
-      <c r="K25" s="14" t="s">
-        <v>98</v>
-      </c>
-      <c r="L25" s="9" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="26" spans="7:12" ht="37.5" x14ac:dyDescent="0.25">
-      <c r="G26" s="14" t="s">
-        <v>191</v>
-      </c>
-      <c r="H26" s="9" t="s">
-        <v>83</v>
-      </c>
-      <c r="K26" s="14" t="s">
-        <v>103</v>
-      </c>
-      <c r="L26" s="9" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="27" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G27" s="24" t="s">
-        <v>92</v>
-      </c>
-      <c r="H27" s="9" t="s">
-        <v>83</v>
-      </c>
-      <c r="K27" s="14" t="s">
-        <v>102</v>
-      </c>
-      <c r="L27" s="9" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="28" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G28" s="24" t="s">
-        <v>142</v>
-      </c>
-      <c r="H28" s="9" t="s">
-        <v>83</v>
-      </c>
-      <c r="K28" s="14" t="s">
-        <v>115</v>
-      </c>
-      <c r="L28" s="9" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="29" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G29" s="24" t="s">
-        <v>90</v>
-      </c>
-      <c r="H29" s="9" t="s">
-        <v>83</v>
-      </c>
-      <c r="K29" s="14" t="s">
-        <v>135</v>
-      </c>
-      <c r="L29" s="9" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="30" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G30" s="24" t="s">
-        <v>121</v>
-      </c>
-      <c r="H30" s="9" t="s">
-        <v>83</v>
-      </c>
-      <c r="K30" s="14" t="s">
-        <v>134</v>
-      </c>
-      <c r="L30" s="9" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="31" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G31" s="24" t="s">
-        <v>147</v>
-      </c>
-      <c r="H31" s="9" t="s">
-        <v>83</v>
-      </c>
-      <c r="K31" s="16" t="s">
-        <v>86</v>
-      </c>
-      <c r="L31" s="9" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="32" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G32" s="24" t="s">
-        <v>189</v>
-      </c>
-      <c r="H32" s="9" t="s">
-        <v>83</v>
-      </c>
-      <c r="K32" s="16" t="s">
-        <v>201</v>
-      </c>
       <c r="L32" s="9" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
     </row>
     <row r="33" spans="7:12" ht="37.5" x14ac:dyDescent="0.25">
       <c r="G33" s="24" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="H33" s="9" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="K33" s="16" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="L33" s="9" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
     </row>
     <row r="34" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G34" s="24" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="H34" s="9" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="K34" s="24" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="L34" s="9" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
     </row>
     <row r="35" spans="7:12" ht="37.5" x14ac:dyDescent="0.25">
       <c r="G35" s="24" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="H35" s="9" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="K35" s="20"/>
       <c r="L35" s="20"/>
     </row>
     <row r="36" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G36" s="24" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="H36" s="9" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="K36" s="20"/>
       <c r="L36" s="20"/>
     </row>
     <row r="37" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G37" s="16" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="H37" s="9" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="K37" s="20"/>
       <c r="L37" s="20"/>
     </row>
     <row r="38" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G38" s="16" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="H38" s="9" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="K38" s="20"/>
       <c r="L38" s="20"/>
     </row>
     <row r="39" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G39" s="16" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="H39" s="9" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="K39" s="20"/>
       <c r="L39" s="20"/>
     </row>
     <row r="40" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G40" s="16" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="H40" s="9" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="K40" s="20"/>
       <c r="L40" s="20"/>
     </row>
     <row r="41" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G41" s="23" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="H41" s="9" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="K41" s="20"/>
       <c r="L41" s="20"/>
     </row>
     <row r="42" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G42" s="23" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="H42" s="9" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="K42" s="20"/>
       <c r="L42" s="20"/>
     </row>
     <row r="43" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G43" s="27" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="H43" s="19" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="K43" s="20"/>
       <c r="L43" s="20"/>
@@ -7851,93 +8370,94 @@
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="4" width="22.5703125" customWidth="1"/>
+    <col min="5" max="5" width="23" customWidth="1"/>
     <col min="7" max="8" width="22.5703125" customWidth="1"/>
     <col min="11" max="12" width="22.5703125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="2" spans="2:12" ht="47.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="35" t="s">
-        <v>230</v>
-      </c>
-      <c r="C2" s="36"/>
-      <c r="D2" s="37"/>
+      <c r="B2" s="34" t="s">
+        <v>227</v>
+      </c>
+      <c r="C2" s="35"/>
+      <c r="D2" s="36"/>
       <c r="G2" s="2" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="H2" s="2" t="s">
         <v>15</v>
       </c>
       <c r="K2" s="2" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="L2" s="2" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="3" spans="2:12" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B3" s="38" t="s">
-        <v>237</v>
-      </c>
-      <c r="C3" s="39"/>
-      <c r="D3" s="40"/>
+      <c r="B3" s="37" t="s">
+        <v>234</v>
+      </c>
+      <c r="C3" s="38"/>
+      <c r="D3" s="39"/>
       <c r="G3" s="6" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="H3" s="6" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="K3" s="29" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="L3" s="6" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
     </row>
     <row r="4" spans="2:12" ht="24" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B4" s="2" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>234</v>
+        <v>231</v>
       </c>
       <c r="G4" s="9" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="H4" s="9" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="K4" s="14" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="L4" s="9" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
     </row>
     <row r="5" spans="2:12" ht="393.75" x14ac:dyDescent="0.25">
       <c r="B5" s="31" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="C5" s="31" t="s">
-        <v>245</v>
+        <v>242</v>
       </c>
       <c r="D5" s="31" t="s">
-        <v>246</v>
+        <v>243</v>
       </c>
       <c r="G5" s="9" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="H5" s="9" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="K5" s="14" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="L5" s="9" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
     </row>
     <row r="6" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
@@ -7945,359 +8465,452 @@
       <c r="C6" s="32"/>
       <c r="D6" s="33"/>
       <c r="G6" s="14" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="H6" s="9" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="K6" s="14" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="L6" s="9" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="7" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="7" spans="2:12" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B7" s="32"/>
       <c r="C7" s="32"/>
       <c r="D7" s="33"/>
       <c r="G7" s="14" t="s">
+        <v>104</v>
+      </c>
+      <c r="H7" s="9" t="s">
+        <v>81</v>
+      </c>
+      <c r="K7" s="14" t="s">
+        <v>84</v>
+      </c>
+      <c r="L7" s="9" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="8" spans="2:12" ht="47.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B8" s="2" t="s">
+        <v>244</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>245</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>246</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>247</v>
+      </c>
+      <c r="G8" s="14" t="s">
+        <v>88</v>
+      </c>
+      <c r="H8" s="9" t="s">
+        <v>81</v>
+      </c>
+      <c r="K8" s="14" t="s">
+        <v>137</v>
+      </c>
+      <c r="L8" s="9" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="9" spans="2:12" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="B9" s="31" t="s">
+        <v>88</v>
+      </c>
+      <c r="C9" s="31" t="s">
+        <v>84</v>
+      </c>
+      <c r="D9" s="42" t="s">
+        <v>257</v>
+      </c>
+      <c r="E9" s="40"/>
+      <c r="G9" s="14" t="s">
+        <v>119</v>
+      </c>
+      <c r="H9" s="9" t="s">
+        <v>81</v>
+      </c>
+      <c r="K9" s="14" t="s">
+        <v>138</v>
+      </c>
+      <c r="L9" s="9" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="10" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B10" s="31" t="s">
+        <v>93</v>
+      </c>
+      <c r="C10" s="31" t="s">
+        <v>258</v>
+      </c>
+      <c r="D10" s="42" t="s">
+        <v>208</v>
+      </c>
+      <c r="E10" s="40"/>
+      <c r="G10" s="16" t="s">
+        <v>102</v>
+      </c>
+      <c r="H10" s="9" t="s">
+        <v>81</v>
+      </c>
+      <c r="K10" s="14" t="s">
+        <v>94</v>
+      </c>
+      <c r="L10" s="9" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="11" spans="2:12" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="B11" s="31" t="s">
+        <v>91</v>
+      </c>
+      <c r="C11" s="31" t="s">
+        <v>85</v>
+      </c>
+      <c r="D11" s="42" t="s">
+        <v>142</v>
+      </c>
+      <c r="E11" s="40"/>
+      <c r="G11" s="16" t="s">
+        <v>157</v>
+      </c>
+      <c r="H11" s="9" t="s">
+        <v>81</v>
+      </c>
+      <c r="K11" s="14" t="s">
+        <v>113</v>
+      </c>
+      <c r="L11" s="9" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="12" spans="2:12" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="B12" s="31" t="s">
+        <v>119</v>
+      </c>
+      <c r="C12" s="31" t="s">
+        <v>89</v>
+      </c>
+      <c r="D12" s="31" t="s">
+        <v>209</v>
+      </c>
+      <c r="E12" s="40"/>
+      <c r="G12" s="16" t="s">
+        <v>148</v>
+      </c>
+      <c r="H12" s="9" t="s">
+        <v>81</v>
+      </c>
+      <c r="K12" s="16" t="s">
+        <v>107</v>
+      </c>
+      <c r="L12" s="9" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="13" spans="2:12" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="B13" s="31" t="s">
+        <v>86</v>
+      </c>
+      <c r="C13" s="31" t="s">
+        <v>83</v>
+      </c>
+      <c r="D13" s="40"/>
+      <c r="E13" s="40"/>
+      <c r="G13" s="16" t="s">
+        <v>146</v>
+      </c>
+      <c r="H13" s="9" t="s">
+        <v>81</v>
+      </c>
+      <c r="K13" s="16" t="s">
+        <v>82</v>
+      </c>
+      <c r="L13" s="9" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="14" spans="2:12" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="B14" s="31" t="s">
+        <v>145</v>
+      </c>
+      <c r="C14" s="31" t="s">
+        <v>108</v>
+      </c>
+      <c r="D14" s="40"/>
+      <c r="E14" s="40"/>
+      <c r="G14" s="16" t="s">
+        <v>151</v>
+      </c>
+      <c r="H14" s="9" t="s">
+        <v>81</v>
+      </c>
+      <c r="K14" s="16" t="s">
+        <v>134</v>
+      </c>
+      <c r="L14" s="9" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="15" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B15" s="31" t="s">
+        <v>202</v>
+      </c>
+      <c r="C15" s="31" t="s">
+        <v>138</v>
+      </c>
+      <c r="D15" s="40"/>
+      <c r="E15" s="40"/>
+      <c r="G15" s="13" t="s">
         <v>106</v>
       </c>
-      <c r="H7" s="9" t="s">
+      <c r="H15" s="9" t="s">
+        <v>81</v>
+      </c>
+      <c r="K15" s="16" t="s">
         <v>83</v>
       </c>
-      <c r="K7" s="14" t="s">
-        <v>86</v>
-      </c>
-      <c r="L7" s="9" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="8" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B8" s="34"/>
-      <c r="C8" s="34"/>
-      <c r="D8" s="33"/>
-      <c r="G8" s="14" t="s">
-        <v>90</v>
-      </c>
-      <c r="H8" s="9" t="s">
-        <v>83</v>
-      </c>
-      <c r="K8" s="14" t="s">
-        <v>139</v>
-      </c>
-      <c r="L8" s="9" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="9" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B9" s="32"/>
-      <c r="C9" s="32"/>
-      <c r="D9" s="33"/>
-      <c r="G9" s="14" t="s">
-        <v>121</v>
-      </c>
-      <c r="H9" s="9" t="s">
-        <v>83</v>
-      </c>
-      <c r="K9" s="14" t="s">
-        <v>140</v>
-      </c>
-      <c r="L9" s="9" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="10" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B10" s="32"/>
-      <c r="C10" s="32"/>
-      <c r="D10" s="33"/>
-      <c r="G10" s="16" t="s">
-        <v>104</v>
-      </c>
-      <c r="H10" s="9" t="s">
-        <v>83</v>
-      </c>
-      <c r="K10" s="14" t="s">
-        <v>96</v>
-      </c>
-      <c r="L10" s="9" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="11" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B11" s="34"/>
-      <c r="C11" s="34"/>
-      <c r="D11" s="33"/>
-      <c r="G11" s="16" t="s">
-        <v>159</v>
-      </c>
-      <c r="H11" s="9" t="s">
-        <v>83</v>
-      </c>
-      <c r="K11" s="14" t="s">
+      <c r="L15" s="9" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="16" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B16" s="31" t="s">
+        <v>95</v>
+      </c>
+      <c r="C16" s="31" t="s">
+        <v>97</v>
+      </c>
+      <c r="D16" s="40"/>
+      <c r="E16" s="40"/>
+      <c r="G16" s="13" t="s">
+        <v>173</v>
+      </c>
+      <c r="H16" s="9" t="s">
+        <v>81</v>
+      </c>
+      <c r="K16" s="16" t="s">
+        <v>89</v>
+      </c>
+      <c r="L16" s="9" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="17" spans="2:12" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="B17" s="31" t="s">
+        <v>141</v>
+      </c>
+      <c r="C17" s="40"/>
+      <c r="D17" s="40"/>
+      <c r="E17" s="40"/>
+      <c r="G17" s="13" t="s">
+        <v>204</v>
+      </c>
+      <c r="H17" s="9" t="s">
+        <v>81</v>
+      </c>
+      <c r="K17" s="16" t="s">
+        <v>105</v>
+      </c>
+      <c r="L17" s="9" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="18" spans="2:12" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="B18" s="31" t="s">
+        <v>251</v>
+      </c>
+      <c r="C18" s="40"/>
+      <c r="D18" s="40"/>
+      <c r="E18" s="40"/>
+      <c r="G18" s="13" t="s">
+        <v>110</v>
+      </c>
+      <c r="H18" s="9" t="s">
+        <v>81</v>
+      </c>
+      <c r="K18" s="16" t="s">
+        <v>103</v>
+      </c>
+      <c r="L18" s="9" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="19" spans="2:12" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="B19" s="40"/>
+      <c r="C19" s="40"/>
+      <c r="D19" s="40"/>
+      <c r="E19" s="40"/>
+      <c r="G19" s="13" t="s">
+        <v>129</v>
+      </c>
+      <c r="H19" s="9" t="s">
+        <v>81</v>
+      </c>
+      <c r="K19" s="16" t="s">
+        <v>200</v>
+      </c>
+      <c r="L19" s="9" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="20" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B20" s="40"/>
+      <c r="C20" s="40"/>
+      <c r="D20" s="40"/>
+      <c r="E20" s="40"/>
+      <c r="G20" s="26" t="s">
+        <v>93</v>
+      </c>
+      <c r="H20" s="9" t="s">
+        <v>81</v>
+      </c>
+      <c r="K20" s="26" t="s">
+        <v>85</v>
+      </c>
+      <c r="L20" s="9" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="21" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B21" s="40"/>
+      <c r="C21" s="40"/>
+      <c r="D21" s="40"/>
+      <c r="E21" s="40"/>
+      <c r="G21" s="26" t="s">
+        <v>141</v>
+      </c>
+      <c r="H21" s="9" t="s">
+        <v>81</v>
+      </c>
+      <c r="K21" s="26" t="s">
+        <v>87</v>
+      </c>
+      <c r="L21" s="9" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="22" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B22" s="40"/>
+      <c r="C22" s="40"/>
+      <c r="D22" s="40"/>
+      <c r="E22" s="40"/>
+      <c r="G22" s="26" t="s">
+        <v>205</v>
+      </c>
+      <c r="H22" s="9" t="s">
+        <v>81</v>
+      </c>
+      <c r="K22" s="24" t="s">
         <v>115</v>
       </c>
-      <c r="L11" s="9" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="12" spans="2:12" ht="37.5" x14ac:dyDescent="0.25">
-      <c r="B12" s="32"/>
-      <c r="C12" s="32"/>
-      <c r="D12" s="33"/>
-      <c r="G12" s="16" t="s">
-        <v>150</v>
-      </c>
-      <c r="H12" s="9" t="s">
-        <v>83</v>
-      </c>
-      <c r="K12" s="16" t="s">
-        <v>109</v>
-      </c>
-      <c r="L12" s="9" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="13" spans="2:12" ht="37.5" x14ac:dyDescent="0.25">
-      <c r="B13" s="32"/>
-      <c r="C13" s="32"/>
-      <c r="D13" s="33"/>
-      <c r="G13" s="16" t="s">
-        <v>148</v>
-      </c>
-      <c r="H13" s="9" t="s">
-        <v>83</v>
-      </c>
-      <c r="K13" s="16" t="s">
-        <v>84</v>
-      </c>
-      <c r="L13" s="9" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="14" spans="2:12" ht="37.5" x14ac:dyDescent="0.25">
-      <c r="B14" s="34"/>
-      <c r="C14" s="34"/>
-      <c r="D14" s="33"/>
-      <c r="G14" s="16" t="s">
-        <v>153</v>
-      </c>
-      <c r="H14" s="9" t="s">
-        <v>83</v>
-      </c>
-      <c r="K14" s="16" t="s">
-        <v>136</v>
-      </c>
-      <c r="L14" s="9" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="15" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B15" s="32"/>
-      <c r="C15" s="32"/>
-      <c r="D15" s="33"/>
-      <c r="G15" s="13" t="s">
-        <v>108</v>
-      </c>
-      <c r="H15" s="9" t="s">
-        <v>83</v>
-      </c>
-      <c r="K15" s="16" t="s">
-        <v>85</v>
-      </c>
-      <c r="L15" s="9" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="16" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B16" s="32"/>
-      <c r="C16" s="32"/>
-      <c r="D16" s="33"/>
-      <c r="G16" s="13" t="s">
-        <v>175</v>
-      </c>
-      <c r="H16" s="9" t="s">
-        <v>83</v>
-      </c>
-      <c r="K16" s="16" t="s">
-        <v>91</v>
-      </c>
-      <c r="L16" s="9" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="17" spans="7:12" ht="37.5" x14ac:dyDescent="0.25">
-      <c r="G17" s="13" t="s">
+      <c r="L22" s="9" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="23" spans="2:12" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="B23" s="40"/>
+      <c r="C23" s="40"/>
+      <c r="D23" s="40"/>
+      <c r="E23" s="40"/>
+      <c r="G23" s="9" t="s">
         <v>206</v>
       </c>
-      <c r="H17" s="9" t="s">
-        <v>83</v>
-      </c>
-      <c r="K17" s="16" t="s">
-        <v>107</v>
-      </c>
-      <c r="L17" s="9" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="18" spans="7:12" ht="37.5" x14ac:dyDescent="0.25">
-      <c r="G18" s="13" t="s">
-        <v>112</v>
-      </c>
-      <c r="H18" s="9" t="s">
-        <v>83</v>
-      </c>
-      <c r="K18" s="16" t="s">
-        <v>105</v>
-      </c>
-      <c r="L18" s="9" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="19" spans="7:12" ht="37.5" x14ac:dyDescent="0.25">
-      <c r="G19" s="13" t="s">
-        <v>131</v>
-      </c>
-      <c r="H19" s="9" t="s">
-        <v>83</v>
-      </c>
-      <c r="K19" s="16" t="s">
-        <v>202</v>
-      </c>
-      <c r="L19" s="9" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="20" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G20" s="26" t="s">
-        <v>95</v>
-      </c>
-      <c r="H20" s="9" t="s">
-        <v>83</v>
-      </c>
-      <c r="K20" s="26" t="s">
-        <v>87</v>
-      </c>
-      <c r="L20" s="9" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="21" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G21" s="26" t="s">
-        <v>143</v>
-      </c>
-      <c r="H21" s="9" t="s">
-        <v>83</v>
-      </c>
-      <c r="K21" s="26" t="s">
-        <v>89</v>
-      </c>
-      <c r="L21" s="9" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="22" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G22" s="26" t="s">
+      <c r="H23" s="9" t="s">
+        <v>81</v>
+      </c>
+      <c r="K23" s="30" t="s">
+        <v>211</v>
+      </c>
+      <c r="L23" s="9" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="24" spans="2:12" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="B24" s="40"/>
+      <c r="C24" s="40"/>
+      <c r="D24" s="40"/>
+      <c r="E24" s="40"/>
+      <c r="G24" s="9" t="s">
         <v>207</v>
       </c>
-      <c r="H22" s="9" t="s">
-        <v>83</v>
-      </c>
-      <c r="K22" s="24" t="s">
-        <v>117</v>
-      </c>
-      <c r="L22" s="9" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="23" spans="7:12" ht="37.5" x14ac:dyDescent="0.25">
-      <c r="G23" s="9" t="s">
-        <v>208</v>
-      </c>
-      <c r="H23" s="9" t="s">
-        <v>83</v>
-      </c>
-      <c r="K23" s="30" t="s">
-        <v>213</v>
-      </c>
-      <c r="L23" s="19" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="24" spans="7:12" ht="37.5" x14ac:dyDescent="0.25">
-      <c r="G24" s="9" t="s">
-        <v>209</v>
-      </c>
       <c r="H24" s="9" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="K24" s="15"/>
       <c r="L24" s="15"/>
     </row>
-    <row r="25" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="25" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G25" s="24" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="H25" s="9" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="K25" s="20"/>
       <c r="L25" s="20"/>
     </row>
-    <row r="26" spans="7:12" ht="37.5" x14ac:dyDescent="0.25">
+    <row r="26" spans="2:12" ht="37.5" x14ac:dyDescent="0.25">
       <c r="G26" s="24" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="H26" s="9" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="K26" s="20"/>
       <c r="L26" s="20"/>
     </row>
-    <row r="27" spans="7:12" ht="37.5" x14ac:dyDescent="0.25">
+    <row r="27" spans="2:12" ht="37.5" x14ac:dyDescent="0.25">
       <c r="G27" s="24" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="H27" s="9" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="K27" s="20"/>
       <c r="L27" s="20"/>
     </row>
-    <row r="28" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="28" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G28" s="24" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="H28" s="9" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="K28" s="20"/>
       <c r="L28" s="20"/>
     </row>
-    <row r="29" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="29" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G29" s="30" t="s">
-        <v>212</v>
-      </c>
-      <c r="H29" s="19" t="s">
-        <v>214</v>
+        <v>210</v>
+      </c>
+      <c r="H29" s="9" t="s">
+        <v>255</v>
       </c>
       <c r="K29" s="20"/>
       <c r="L29" s="20"/>
     </row>
-    <row r="30" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="30" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G30" s="15"/>
       <c r="H30" s="15"/>
       <c r="K30" s="20"/>
       <c r="L30" s="20"/>
     </row>
-    <row r="31" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="31" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G31" s="20"/>
       <c r="H31" s="20"/>
       <c r="K31" s="20"/>
       <c r="L31" s="20"/>
     </row>
-    <row r="32" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="32" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G32" s="20"/>
       <c r="H32" s="20"/>
       <c r="K32" s="20"/>
@@ -8439,93 +9052,94 @@
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="4" width="22.5703125" customWidth="1"/>
+    <col min="5" max="5" width="23.140625" customWidth="1"/>
     <col min="7" max="8" width="22.5703125" customWidth="1"/>
     <col min="11" max="12" width="22.5703125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="2" spans="2:12" ht="47.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="35" t="s">
-        <v>230</v>
-      </c>
-      <c r="C2" s="36"/>
-      <c r="D2" s="37"/>
+      <c r="B2" s="34" t="s">
+        <v>227</v>
+      </c>
+      <c r="C2" s="35"/>
+      <c r="D2" s="36"/>
       <c r="G2" s="2" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="H2" s="2" t="s">
         <v>15</v>
       </c>
       <c r="K2" s="2" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="L2" s="2" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="3" spans="2:12" ht="24" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B3" s="38" t="s">
-        <v>231</v>
-      </c>
-      <c r="C3" s="39"/>
-      <c r="D3" s="40"/>
+      <c r="B3" s="37" t="s">
+        <v>228</v>
+      </c>
+      <c r="C3" s="38"/>
+      <c r="D3" s="39"/>
       <c r="G3" s="21" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="H3" s="6" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="K3" s="21" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="L3" s="6" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
     </row>
     <row r="4" spans="2:12" ht="24" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B4" s="2" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>234</v>
+        <v>231</v>
       </c>
       <c r="G4" s="13" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="H4" s="9" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="K4" s="13" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="L4" s="9" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
     </row>
     <row r="5" spans="2:12" ht="75" x14ac:dyDescent="0.25">
       <c r="B5" s="31" t="s">
-        <v>235</v>
+        <v>232</v>
       </c>
       <c r="C5" s="31" t="s">
-        <v>235</v>
+        <v>232</v>
       </c>
       <c r="D5" s="31" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="G5" s="13" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="H5" s="9" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="K5" s="13" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="L5" s="9" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
     </row>
     <row r="6" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
@@ -8533,466 +9147,555 @@
       <c r="C6" s="32"/>
       <c r="D6" s="33"/>
       <c r="G6" s="13" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="H6" s="9" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="K6" s="13" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="L6" s="9" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="7" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="7" spans="2:12" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B7" s="32"/>
       <c r="C7" s="32"/>
       <c r="D7" s="33"/>
       <c r="G7" s="13" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="H7" s="9" t="s">
+        <v>81</v>
+      </c>
+      <c r="K7" s="13" t="s">
+        <v>105</v>
+      </c>
+      <c r="L7" s="9" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="8" spans="2:12" ht="47.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B8" s="2" t="s">
+        <v>244</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>245</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>246</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>247</v>
+      </c>
+      <c r="G8" s="13" t="s">
+        <v>212</v>
+      </c>
+      <c r="H8" s="9" t="s">
+        <v>81</v>
+      </c>
+      <c r="K8" s="13" t="s">
+        <v>85</v>
+      </c>
+      <c r="L8" s="9" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="9" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B9" s="31" t="s">
+        <v>111</v>
+      </c>
+      <c r="C9" s="31" t="s">
+        <v>84</v>
+      </c>
+      <c r="D9" s="40"/>
+      <c r="E9" s="42" t="s">
+        <v>89</v>
+      </c>
+      <c r="G9" s="13" t="s">
+        <v>88</v>
+      </c>
+      <c r="H9" s="9" t="s">
+        <v>81</v>
+      </c>
+      <c r="K9" s="13" t="s">
+        <v>89</v>
+      </c>
+      <c r="L9" s="9" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="10" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B10" s="31" t="s">
+        <v>214</v>
+      </c>
+      <c r="C10" s="31" t="s">
+        <v>87</v>
+      </c>
+      <c r="D10" s="40"/>
+      <c r="E10" s="41" t="s">
+        <v>96</v>
+      </c>
+      <c r="G10" s="13" t="s">
+        <v>102</v>
+      </c>
+      <c r="H10" s="9" t="s">
+        <v>81</v>
+      </c>
+      <c r="K10" s="13" t="s">
+        <v>115</v>
+      </c>
+      <c r="L10" s="9" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="11" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B11" s="31" t="s">
+        <v>259</v>
+      </c>
+      <c r="C11" s="31" t="s">
+        <v>85</v>
+      </c>
+      <c r="D11" s="40"/>
+      <c r="E11" s="42" t="s">
+        <v>108</v>
+      </c>
+      <c r="G11" s="13" t="s">
+        <v>91</v>
+      </c>
+      <c r="H11" s="9" t="s">
+        <v>81</v>
+      </c>
+      <c r="K11" s="13" t="s">
+        <v>94</v>
+      </c>
+      <c r="L11" s="9" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="12" spans="2:12" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="B12" s="31" t="s">
+        <v>118</v>
+      </c>
+      <c r="C12" s="31" t="s">
+        <v>138</v>
+      </c>
+      <c r="D12" s="40"/>
+      <c r="E12" s="42" t="s">
+        <v>97</v>
+      </c>
+      <c r="G12" s="9" t="s">
+        <v>213</v>
+      </c>
+      <c r="H12" s="9" t="s">
+        <v>81</v>
+      </c>
+      <c r="K12" s="13" t="s">
+        <v>133</v>
+      </c>
+      <c r="L12" s="9" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="13" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B13" s="31" t="s">
+        <v>254</v>
+      </c>
+      <c r="C13" s="40"/>
+      <c r="D13" s="40"/>
+      <c r="E13" s="31" t="s">
+        <v>109</v>
+      </c>
+      <c r="G13" s="26" t="s">
+        <v>90</v>
+      </c>
+      <c r="H13" s="9" t="s">
+        <v>81</v>
+      </c>
+      <c r="K13" s="13" t="s">
+        <v>221</v>
+      </c>
+      <c r="L13" s="9" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="14" spans="2:12" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="B14" s="31" t="s">
+        <v>142</v>
+      </c>
+      <c r="C14" s="40"/>
+      <c r="D14" s="40"/>
+      <c r="E14" s="40"/>
+      <c r="G14" s="26" t="s">
+        <v>141</v>
+      </c>
+      <c r="H14" s="9" t="s">
+        <v>81</v>
+      </c>
+      <c r="K14" s="17" t="s">
+        <v>82</v>
+      </c>
+      <c r="L14" s="9" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="15" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B15" s="31" t="s">
+        <v>93</v>
+      </c>
+      <c r="C15" s="40"/>
+      <c r="D15" s="40"/>
+      <c r="E15" s="40"/>
+      <c r="G15" s="26" t="s">
+        <v>99</v>
+      </c>
+      <c r="H15" s="9" t="s">
+        <v>81</v>
+      </c>
+      <c r="K15" s="17" t="s">
+        <v>97</v>
+      </c>
+      <c r="L15" s="9" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="16" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B16" s="31" t="s">
+        <v>95</v>
+      </c>
+      <c r="C16" s="40"/>
+      <c r="D16" s="40"/>
+      <c r="E16" s="40"/>
+      <c r="G16" s="26" t="s">
+        <v>111</v>
+      </c>
+      <c r="H16" s="9" t="s">
+        <v>81</v>
+      </c>
+      <c r="K16" s="17" t="s">
+        <v>138</v>
+      </c>
+      <c r="L16" s="9" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="17" spans="2:12" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="B17" s="31" t="s">
+        <v>158</v>
+      </c>
+      <c r="C17" s="40"/>
+      <c r="D17" s="40"/>
+      <c r="E17" s="40"/>
+      <c r="G17" s="26" t="s">
+        <v>178</v>
+      </c>
+      <c r="H17" s="9" t="s">
+        <v>81</v>
+      </c>
+      <c r="K17" s="17" t="s">
         <v>83</v>
       </c>
-      <c r="K7" s="13" t="s">
+      <c r="L17" s="9" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="18" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B18" s="31" t="s">
+        <v>102</v>
+      </c>
+      <c r="C18" s="40"/>
+      <c r="D18" s="40"/>
+      <c r="E18" s="40"/>
+      <c r="G18" s="26" t="s">
+        <v>123</v>
+      </c>
+      <c r="H18" s="9" t="s">
+        <v>81</v>
+      </c>
+      <c r="K18" s="26" t="s">
+        <v>98</v>
+      </c>
+      <c r="L18" s="9" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="19" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B19" s="31" t="s">
+        <v>145</v>
+      </c>
+      <c r="C19" s="40"/>
+      <c r="D19" s="40"/>
+      <c r="E19" s="40"/>
+      <c r="G19" s="26" t="s">
+        <v>145</v>
+      </c>
+      <c r="H19" s="9" t="s">
+        <v>81</v>
+      </c>
+      <c r="K19" s="26" t="s">
         <v>107</v>
       </c>
-      <c r="L7" s="9" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="8" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B8" s="34"/>
-      <c r="C8" s="34"/>
-      <c r="D8" s="33"/>
-      <c r="G8" s="13" t="s">
+      <c r="L19" s="9" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="20" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B20" s="40"/>
+      <c r="C20" s="40"/>
+      <c r="D20" s="40"/>
+      <c r="E20" s="40"/>
+      <c r="G20" s="26" t="s">
+        <v>174</v>
+      </c>
+      <c r="H20" s="9" t="s">
+        <v>81</v>
+      </c>
+      <c r="K20" s="26" t="s">
+        <v>103</v>
+      </c>
+      <c r="L20" s="9" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="21" spans="2:12" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="B21" s="40"/>
+      <c r="C21" s="40"/>
+      <c r="D21" s="40"/>
+      <c r="E21" s="40"/>
+      <c r="G21" s="26" t="s">
+        <v>204</v>
+      </c>
+      <c r="H21" s="9" t="s">
+        <v>81</v>
+      </c>
+      <c r="K21" s="26" t="s">
+        <v>200</v>
+      </c>
+      <c r="L21" s="9" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="22" spans="2:12" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="B22" s="40"/>
+      <c r="C22" s="40"/>
+      <c r="D22" s="40"/>
+      <c r="E22" s="40"/>
+      <c r="G22" s="26" t="s">
         <v>215</v>
       </c>
-      <c r="H8" s="9" t="s">
-        <v>83</v>
-      </c>
-      <c r="K8" s="13" t="s">
-        <v>87</v>
-      </c>
-      <c r="L8" s="9" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="9" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B9" s="32"/>
-      <c r="C9" s="32"/>
-      <c r="D9" s="33"/>
-      <c r="G9" s="13" t="s">
-        <v>90</v>
-      </c>
-      <c r="H9" s="9" t="s">
-        <v>83</v>
-      </c>
-      <c r="K9" s="13" t="s">
-        <v>91</v>
-      </c>
-      <c r="L9" s="9" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="10" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B10" s="32"/>
-      <c r="C10" s="32"/>
-      <c r="D10" s="33"/>
-      <c r="G10" s="13" t="s">
+      <c r="H22" s="9" t="s">
+        <v>81</v>
+      </c>
+      <c r="K22" s="26" t="s">
+        <v>134</v>
+      </c>
+      <c r="L22" s="9" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="23" spans="2:12" ht="56.25" x14ac:dyDescent="0.25">
+      <c r="B23" s="40"/>
+      <c r="C23" s="40"/>
+      <c r="D23" s="40"/>
+      <c r="E23" s="40"/>
+      <c r="G23" s="26" t="s">
+        <v>185</v>
+      </c>
+      <c r="H23" s="9" t="s">
+        <v>81</v>
+      </c>
+      <c r="K23" s="26" t="s">
+        <v>108</v>
+      </c>
+      <c r="L23" s="9" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="24" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B24" s="40"/>
+      <c r="C24" s="40"/>
+      <c r="D24" s="40"/>
+      <c r="E24" s="40"/>
+      <c r="G24" s="26" t="s">
+        <v>214</v>
+      </c>
+      <c r="H24" s="9" t="s">
+        <v>81</v>
+      </c>
+      <c r="K24" s="16" t="s">
+        <v>92</v>
+      </c>
+      <c r="L24" s="9" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="25" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G25" s="26" t="s">
+        <v>188</v>
+      </c>
+      <c r="H25" s="9" t="s">
+        <v>196</v>
+      </c>
+      <c r="K25" s="16" t="s">
+        <v>96</v>
+      </c>
+      <c r="L25" s="9" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="26" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G26" s="26" t="s">
+        <v>190</v>
+      </c>
+      <c r="H26" s="9" t="s">
+        <v>196</v>
+      </c>
+      <c r="K26" s="16" t="s">
+        <v>101</v>
+      </c>
+      <c r="L26" s="9" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="27" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G27" s="26" t="s">
+        <v>202</v>
+      </c>
+      <c r="H27" s="9" t="s">
+        <v>196</v>
+      </c>
+      <c r="K27" s="16" t="s">
+        <v>109</v>
+      </c>
+      <c r="L27" s="9" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="28" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G28" s="16" t="s">
+        <v>119</v>
+      </c>
+      <c r="H28" s="9" t="s">
+        <v>81</v>
+      </c>
+      <c r="K28" s="16" t="s">
+        <v>135</v>
+      </c>
+      <c r="L28" s="9" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="29" spans="2:12" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="G29" s="16" t="s">
+        <v>187</v>
+      </c>
+      <c r="H29" s="9" t="s">
+        <v>81</v>
+      </c>
+      <c r="K29" s="23" t="s">
+        <v>168</v>
+      </c>
+      <c r="L29" s="9" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="30" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G30" s="16" t="s">
+        <v>122</v>
+      </c>
+      <c r="H30" s="9" t="s">
+        <v>81</v>
+      </c>
+      <c r="K30" s="14" t="s">
+        <v>113</v>
+      </c>
+      <c r="L30" s="9" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="31" spans="2:12" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="G31" s="9" t="s">
+        <v>216</v>
+      </c>
+      <c r="H31" s="9" t="s">
+        <v>81</v>
+      </c>
+      <c r="K31" s="14" t="s">
+        <v>222</v>
+      </c>
+      <c r="L31" s="9" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="32" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G32" s="16" t="s">
         <v>104</v>
       </c>
-      <c r="H10" s="9" t="s">
-        <v>83</v>
-      </c>
-      <c r="K10" s="13" t="s">
-        <v>117</v>
-      </c>
-      <c r="L10" s="9" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="11" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B11" s="34"/>
-      <c r="C11" s="34"/>
-      <c r="D11" s="33"/>
-      <c r="G11" s="13" t="s">
-        <v>93</v>
-      </c>
-      <c r="H11" s="9" t="s">
-        <v>83</v>
-      </c>
-      <c r="K11" s="13" t="s">
-        <v>96</v>
-      </c>
-      <c r="L11" s="9" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="12" spans="2:12" ht="37.5" x14ac:dyDescent="0.25">
-      <c r="B12" s="32"/>
-      <c r="C12" s="32"/>
-      <c r="D12" s="33"/>
-      <c r="G12" s="9" t="s">
-        <v>216</v>
-      </c>
-      <c r="H12" s="9" t="s">
-        <v>83</v>
-      </c>
-      <c r="K12" s="13" t="s">
-        <v>135</v>
-      </c>
-      <c r="L12" s="9" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="13" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B13" s="32"/>
-      <c r="C13" s="32"/>
-      <c r="D13" s="33"/>
-      <c r="G13" s="26" t="s">
-        <v>92</v>
-      </c>
-      <c r="H13" s="9" t="s">
-        <v>83</v>
-      </c>
-      <c r="K13" s="13" t="s">
-        <v>224</v>
-      </c>
-      <c r="L13" s="9" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="14" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B14" s="34"/>
-      <c r="C14" s="34"/>
-      <c r="D14" s="33"/>
-      <c r="G14" s="26" t="s">
-        <v>143</v>
-      </c>
-      <c r="H14" s="9" t="s">
-        <v>83</v>
-      </c>
-      <c r="K14" s="17" t="s">
-        <v>84</v>
-      </c>
-      <c r="L14" s="9" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="15" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B15" s="32"/>
-      <c r="C15" s="32"/>
-      <c r="D15" s="33"/>
-      <c r="G15" s="26" t="s">
-        <v>101</v>
-      </c>
-      <c r="H15" s="9" t="s">
-        <v>83</v>
-      </c>
-      <c r="K15" s="17" t="s">
-        <v>99</v>
-      </c>
-      <c r="L15" s="9" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="16" spans="2:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B16" s="32"/>
-      <c r="C16" s="32"/>
-      <c r="D16" s="33"/>
-      <c r="G16" s="26" t="s">
-        <v>113</v>
-      </c>
-      <c r="H16" s="9" t="s">
-        <v>83</v>
-      </c>
-      <c r="K16" s="17" t="s">
-        <v>140</v>
-      </c>
-      <c r="L16" s="9" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="17" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G17" s="26" t="s">
-        <v>180</v>
-      </c>
-      <c r="H17" s="9" t="s">
-        <v>83</v>
-      </c>
-      <c r="K17" s="17" t="s">
-        <v>85</v>
-      </c>
-      <c r="L17" s="9" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="18" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G18" s="26" t="s">
-        <v>125</v>
-      </c>
-      <c r="H18" s="9" t="s">
-        <v>83</v>
-      </c>
-      <c r="K18" s="26" t="s">
-        <v>100</v>
-      </c>
-      <c r="L18" s="9" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="19" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G19" s="26" t="s">
-        <v>147</v>
-      </c>
-      <c r="H19" s="9" t="s">
-        <v>83</v>
-      </c>
-      <c r="K19" s="26" t="s">
-        <v>109</v>
-      </c>
-      <c r="L19" s="9" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="20" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G20" s="26" t="s">
-        <v>176</v>
-      </c>
-      <c r="H20" s="9" t="s">
-        <v>83</v>
-      </c>
-      <c r="K20" s="26" t="s">
-        <v>105</v>
-      </c>
-      <c r="L20" s="9" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="21" spans="7:12" ht="37.5" x14ac:dyDescent="0.25">
-      <c r="G21" s="26" t="s">
-        <v>206</v>
-      </c>
-      <c r="H21" s="9" t="s">
-        <v>83</v>
-      </c>
-      <c r="K21" s="26" t="s">
-        <v>202</v>
-      </c>
-      <c r="L21" s="9" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="22" spans="7:12" ht="37.5" x14ac:dyDescent="0.25">
-      <c r="G22" s="26" t="s">
-        <v>218</v>
-      </c>
-      <c r="H22" s="9" t="s">
-        <v>83</v>
-      </c>
-      <c r="K22" s="26" t="s">
-        <v>136</v>
-      </c>
-      <c r="L22" s="9" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="23" spans="7:12" ht="56.25" x14ac:dyDescent="0.25">
-      <c r="G23" s="26" t="s">
-        <v>187</v>
-      </c>
-      <c r="H23" s="9" t="s">
-        <v>83</v>
-      </c>
-      <c r="K23" s="26" t="s">
-        <v>110</v>
-      </c>
-      <c r="L23" s="9" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="24" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G24" s="26" t="s">
-        <v>217</v>
-      </c>
-      <c r="H24" s="9" t="s">
-        <v>83</v>
-      </c>
-      <c r="K24" s="16" t="s">
-        <v>94</v>
-      </c>
-      <c r="L24" s="9" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="25" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G25" s="26" t="s">
-        <v>190</v>
-      </c>
-      <c r="H25" s="9" t="s">
-        <v>198</v>
-      </c>
-      <c r="K25" s="16" t="s">
-        <v>98</v>
-      </c>
-      <c r="L25" s="9" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="26" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G26" s="26" t="s">
-        <v>192</v>
-      </c>
-      <c r="H26" s="9" t="s">
-        <v>198</v>
-      </c>
-      <c r="K26" s="16" t="s">
-        <v>103</v>
-      </c>
-      <c r="L26" s="9" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="27" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G27" s="26" t="s">
-        <v>204</v>
-      </c>
-      <c r="H27" s="9" t="s">
-        <v>198</v>
-      </c>
-      <c r="K27" s="16" t="s">
-        <v>111</v>
-      </c>
-      <c r="L27" s="9" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="28" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G28" s="16" t="s">
-        <v>121</v>
-      </c>
-      <c r="H28" s="9" t="s">
-        <v>83</v>
-      </c>
-      <c r="K28" s="16" t="s">
-        <v>137</v>
-      </c>
-      <c r="L28" s="9" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="29" spans="7:12" ht="37.5" x14ac:dyDescent="0.25">
-      <c r="G29" s="16" t="s">
-        <v>189</v>
-      </c>
-      <c r="H29" s="9" t="s">
-        <v>83</v>
-      </c>
-      <c r="K29" s="23" t="s">
-        <v>170</v>
-      </c>
-      <c r="L29" s="9" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="30" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G30" s="16" t="s">
-        <v>124</v>
-      </c>
-      <c r="H30" s="9" t="s">
-        <v>83</v>
-      </c>
-      <c r="K30" s="14" t="s">
-        <v>115</v>
-      </c>
-      <c r="L30" s="9" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="31" spans="7:12" ht="37.5" x14ac:dyDescent="0.25">
-      <c r="G31" s="9" t="s">
-        <v>219</v>
-      </c>
-      <c r="H31" s="9" t="s">
-        <v>83</v>
-      </c>
-      <c r="K31" s="14" t="s">
-        <v>225</v>
-      </c>
-      <c r="L31" s="9" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="32" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="G32" s="16" t="s">
-        <v>106</v>
-      </c>
       <c r="H32" s="9" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="K32" s="14" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="L32" s="9" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
     </row>
     <row r="33" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G33" s="14" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="H33" s="9" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="K33" s="14" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="L33" s="9" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
     </row>
     <row r="34" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G34" s="23" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="H34" s="9" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="K34" s="18" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
       <c r="L34" s="19" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
     </row>
     <row r="35" spans="7:12" ht="37.5" x14ac:dyDescent="0.25">
       <c r="G35" s="23" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="H35" s="9" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="K35" s="15"/>
       <c r="L35" s="15"/>
     </row>
     <row r="36" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G36" s="23" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="H36" s="9" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="K36" s="20"/>
       <c r="L36" s="20"/>
     </row>
     <row r="37" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
       <c r="G37" s="24" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="H37" s="9" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="K37" s="20"/>
       <c r="L37" s="20"/>
